--- a/Durability I-V figure/tafel plot alt/Overpotential DATA raw alt/O2 BP/BOL/Edited/CN BM 1.5bp O2_edited.xlsx
+++ b/Durability I-V figure/tafel plot alt/Overpotential DATA raw alt/O2 BP/BOL/Edited/CN BM 1.5bp O2_edited.xlsx
@@ -461,7 +461,7 @@
   <cols>
     <col width="12.25" customWidth="1" style="1" min="10" max="10"/>
     <col width="13.625" bestFit="1" customWidth="1" style="1" min="11" max="11"/>
-    <col width="18.375" bestFit="1" customWidth="1" style="1" min="28" max="28"/>
+    <col width="14" bestFit="1" customWidth="1" style="1" min="28" max="28"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -627,7 +627,7 @@
         </is>
       </c>
       <c r="AB3" s="0" t="n">
-        <v>-0.33992</v>
+        <v>-0.54984</v>
       </c>
       <c r="AC3" s="0" t="inlineStr">
         <is>
@@ -637,20 +637,20 @@
     </row>
     <row r="4">
       <c r="A4" s="0" t="n">
-        <v>0.06409655</v>
+        <v>0.05238535</v>
       </c>
       <c r="B4" s="0" t="n">
-        <v>0.85166</v>
+        <v>0.85347</v>
       </c>
       <c r="C4" s="0">
         <f>A4*B4</f>
         <v/>
       </c>
       <c r="D4" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E4" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F4" s="0">
         <f>A4*200</f>
@@ -700,7 +700,7 @@
         </is>
       </c>
       <c r="S4" s="0" t="n">
-        <v>-0.535</v>
+        <v>-0.5422</v>
       </c>
       <c r="V4" s="0" t="n">
         <v>-6</v>
@@ -717,7 +717,7 @@
         <v/>
       </c>
       <c r="AB4" s="0" t="n">
-        <v>9.3362</v>
+        <v>14.18899</v>
       </c>
       <c r="AC4" s="0" t="inlineStr">
         <is>
@@ -727,20 +727,20 @@
     </row>
     <row r="5">
       <c r="A5" s="0" t="n">
-        <v>0.11807</v>
+        <v>0.1109414</v>
       </c>
       <c r="B5" s="0" t="n">
-        <v>0.84292</v>
+        <v>0.8453000000000001</v>
       </c>
       <c r="C5" s="0">
         <f>A5*B5</f>
         <v/>
       </c>
       <c r="D5" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E5" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F5" s="0">
         <f>A5*200</f>
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="S5" s="0" t="n">
-        <v>-0.0418</v>
+        <v>-0.0455</v>
       </c>
       <c r="V5" s="0" t="n">
         <v>-5.9</v>
@@ -809,20 +809,20 @@
     </row>
     <row r="6">
       <c r="A6" s="0" t="n">
-        <v>0.17204345</v>
+        <v>0.16593325</v>
       </c>
       <c r="B6" s="0" t="n">
-        <v>0.83316</v>
+        <v>0.83486</v>
       </c>
       <c r="C6" s="0">
         <f>A6*B6</f>
         <v/>
       </c>
       <c r="D6" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E6" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F6" s="0">
         <f>A6*200</f>
@@ -888,20 +888,20 @@
     </row>
     <row r="7">
       <c r="A7" s="0" t="n">
-        <v>0.2239801</v>
+        <v>0.2183791</v>
       </c>
       <c r="B7" s="0" t="n">
-        <v>0.82478</v>
+        <v>0.8268799999999999</v>
       </c>
       <c r="C7" s="0">
         <f>A7*B7</f>
         <v/>
       </c>
       <c r="D7" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E7" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F7" s="0">
         <f>A7*200</f>
@@ -971,20 +971,20 @@
     </row>
     <row r="8">
       <c r="A8" s="0" t="n">
-        <v>0.27489845</v>
+        <v>0.27133415</v>
       </c>
       <c r="B8" s="0" t="n">
-        <v>0.81781</v>
+        <v>0.81901</v>
       </c>
       <c r="C8" s="0">
         <f>A8*B8</f>
         <v/>
       </c>
       <c r="D8" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E8" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F8" s="0">
         <f>A8*200</f>
@@ -1045,20 +1045,20 @@
     </row>
     <row r="9">
       <c r="A9" s="0" t="n">
-        <v>0.3253076</v>
+        <v>0.3222525</v>
       </c>
       <c r="B9" s="0" t="n">
-        <v>0.81074</v>
+        <v>0.81246</v>
       </c>
       <c r="C9" s="0">
         <f>A9*B9</f>
         <v/>
       </c>
       <c r="D9" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E9" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F9" s="0">
         <f>A9*200</f>
@@ -1122,7 +1122,7 @@
         </is>
       </c>
       <c r="AC9" s="0" t="n">
-        <v>0.0317</v>
+        <v>0.03283</v>
       </c>
     </row>
     <row r="10">
@@ -1130,17 +1130,17 @@
         <v>0.37571675</v>
       </c>
       <c r="B10" s="0" t="n">
-        <v>0.80532</v>
+        <v>0.80647</v>
       </c>
       <c r="C10" s="0">
         <f>A10*B10</f>
         <v/>
       </c>
       <c r="D10" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E10" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F10" s="0">
         <f>A10*200</f>
@@ -1201,20 +1201,20 @@
     </row>
     <row r="11">
       <c r="A11" s="0" t="n">
-        <v>0.42714425</v>
+        <v>0.43019935</v>
       </c>
       <c r="B11" s="0" t="n">
-        <v>0.79935</v>
+        <v>0.8004</v>
       </c>
       <c r="C11" s="0">
         <f>A11*B11</f>
         <v/>
       </c>
       <c r="D11" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E11" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F11" s="0">
         <f>A11*200</f>
@@ -1284,20 +1284,20 @@
     </row>
     <row r="12">
       <c r="A12" s="0" t="n">
-        <v>0.47806255</v>
+        <v>0.48060845</v>
       </c>
       <c r="B12" s="0" t="n">
-        <v>0.79373</v>
+        <v>0.79478</v>
       </c>
       <c r="C12" s="0">
         <f>A12*B12</f>
         <v/>
       </c>
       <c r="D12" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E12" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F12" s="0">
         <f>A12*200</f>
@@ -1362,20 +1362,20 @@
     </row>
     <row r="13">
       <c r="A13" s="0" t="n">
-        <v>0.53203605</v>
+        <v>0.53152685</v>
       </c>
       <c r="B13" s="0" t="n">
-        <v>0.78896</v>
+        <v>0.78961</v>
       </c>
       <c r="C13" s="0">
         <f>A13*B13</f>
         <v/>
       </c>
       <c r="D13" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E13" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F13" s="0">
         <f>A13*200</f>
@@ -1436,20 +1436,20 @@
     </row>
     <row r="14">
       <c r="A14" s="0" t="n">
-        <v>0.5834635</v>
+        <v>0.58193595</v>
       </c>
       <c r="B14" s="0" t="n">
-        <v>0.7834</v>
+        <v>0.78524</v>
       </c>
       <c r="C14" s="0">
         <f>A14*B14</f>
         <v/>
       </c>
       <c r="D14" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E14" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F14" s="0">
         <f>A14*200</f>
@@ -1510,20 +1510,20 @@
     </row>
     <row r="15">
       <c r="A15" s="0" t="n">
-        <v>0.6338726</v>
+        <v>0.6354002</v>
       </c>
       <c r="B15" s="0" t="n">
-        <v>0.77886</v>
+        <v>0.7806</v>
       </c>
       <c r="C15" s="0">
         <f>A15*B15</f>
         <v/>
       </c>
       <c r="D15" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E15" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F15" s="0">
         <f>A15*200</f>
@@ -1584,20 +1584,20 @@
     </row>
     <row r="16">
       <c r="A16" s="0" t="n">
-        <v>0.68682775</v>
+        <v>0.68784615</v>
       </c>
       <c r="B16" s="0" t="n">
-        <v>0.77454</v>
+        <v>0.77584</v>
       </c>
       <c r="C16" s="0">
         <f>A16*B16</f>
         <v/>
       </c>
       <c r="D16" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E16" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F16" s="0">
         <f>A16*200</f>
@@ -1658,20 +1658,20 @@
     </row>
     <row r="17">
       <c r="A17" s="0" t="n">
-        <v>0.73723695</v>
+        <v>0.73825525</v>
       </c>
       <c r="B17" s="0" t="n">
-        <v>0.76977</v>
+        <v>0.77151</v>
       </c>
       <c r="C17" s="0">
         <f>A17*B17</f>
         <v/>
       </c>
       <c r="D17" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E17" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F17" s="0">
         <f>A17*200</f>
@@ -1732,20 +1732,20 @@
     </row>
     <row r="18">
       <c r="A18" s="0" t="n">
-        <v>0.787646</v>
+        <v>0.7896827</v>
       </c>
       <c r="B18" s="0" t="n">
-        <v>0.7658</v>
+        <v>0.76752</v>
       </c>
       <c r="C18" s="0">
         <f>A18*B18</f>
         <v/>
       </c>
       <c r="D18" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E18" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F18" s="0">
         <f>A18*200</f>
@@ -1806,20 +1806,20 @@
     </row>
     <row r="19">
       <c r="A19" s="0" t="n">
-        <v>0.8395827</v>
+        <v>0.8426378</v>
       </c>
       <c r="B19" s="0" t="n">
-        <v>0.76156</v>
+        <v>0.76311</v>
       </c>
       <c r="C19" s="0">
         <f>A19*B19</f>
         <v/>
       </c>
       <c r="D19" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E19" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F19" s="0">
         <f>A19*200</f>
@@ -1883,17 +1883,17 @@
         <v>0.89355615</v>
       </c>
       <c r="B20" s="0" t="n">
-        <v>0.75784</v>
+        <v>0.7593299999999999</v>
       </c>
       <c r="C20" s="0">
         <f>A20*B20</f>
         <v/>
       </c>
       <c r="D20" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E20" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F20" s="0">
         <f>A20*200</f>
@@ -1954,20 +1954,20 @@
     </row>
     <row r="21">
       <c r="A21" s="0" t="n">
-        <v>0.94447455</v>
+        <v>0.9454928</v>
       </c>
       <c r="B21" s="0" t="n">
-        <v>0.75329</v>
+        <v>0.75549</v>
       </c>
       <c r="C21" s="0">
         <f>A21*B21</f>
         <v/>
       </c>
       <c r="D21" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E21" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F21" s="0">
         <f>A21*200</f>
@@ -2028,20 +2028,20 @@
     </row>
     <row r="22">
       <c r="A22" s="0" t="n">
-        <v>0.99488365</v>
+        <v>0.99895705</v>
       </c>
       <c r="B22" s="0" t="n">
-        <v>0.74974</v>
+        <v>0.75161</v>
       </c>
       <c r="C22" s="0">
         <f>A22*B22</f>
         <v/>
       </c>
       <c r="D22" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E22" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F22" s="0">
         <f>A22*200</f>
@@ -2102,20 +2102,20 @@
     </row>
     <row r="23">
       <c r="A23" s="0" t="n">
-        <v>1.0463113</v>
+        <v>1.0493663</v>
       </c>
       <c r="B23" s="0" t="n">
-        <v>0.74652</v>
+        <v>0.74795</v>
       </c>
       <c r="C23" s="0">
         <f>A23*B23</f>
         <v/>
       </c>
       <c r="D23" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E23" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F23" s="0">
         <f>A23*200</f>
@@ -2176,20 +2176,20 @@
     </row>
     <row r="24">
       <c r="A24" s="0" t="n">
-        <v>1.0967203</v>
+        <v>1.1002845</v>
       </c>
       <c r="B24" s="0" t="n">
-        <v>0.74268</v>
+        <v>0.74449</v>
       </c>
       <c r="C24" s="0">
         <f>A24*B24</f>
         <v/>
       </c>
       <c r="D24" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E24" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F24" s="0">
         <f>A24*200</f>
@@ -2250,20 +2250,20 @@
     </row>
     <row r="25">
       <c r="A25" s="0" t="n">
-        <v>1.1471295</v>
+        <v>1.1532396</v>
       </c>
       <c r="B25" s="0" t="n">
-        <v>0.73905</v>
+        <v>0.7410600000000001</v>
       </c>
       <c r="C25" s="0">
         <f>A25*B25</f>
         <v/>
       </c>
       <c r="D25" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E25" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F25" s="0">
         <f>A25*200</f>
@@ -2324,20 +2324,20 @@
     </row>
     <row r="26">
       <c r="A26" s="0" t="n">
-        <v>1.1980479</v>
+        <v>1.2072131</v>
       </c>
       <c r="B26" s="0" t="n">
-        <v>0.73548</v>
+        <v>0.7373499999999999</v>
       </c>
       <c r="C26" s="0">
         <f>A26*B26</f>
         <v/>
       </c>
       <c r="D26" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E26" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F26" s="0">
         <f>A26*200</f>
@@ -2398,20 +2398,20 @@
     </row>
     <row r="27">
       <c r="A27" s="0" t="n">
-        <v>1.248457</v>
+        <v>1.2596588</v>
       </c>
       <c r="B27" s="0" t="n">
-        <v>0.7322</v>
+        <v>0.7339</v>
       </c>
       <c r="C27" s="0">
         <f>A27*B27</f>
         <v/>
       </c>
       <c r="D27" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E27" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F27" s="0">
         <f>A27*200</f>
@@ -2472,20 +2472,20 @@
     </row>
     <row r="28">
       <c r="A28" s="0" t="n">
-        <v>1.3019213</v>
+        <v>1.3131232</v>
       </c>
       <c r="B28" s="0" t="n">
-        <v>0.7291</v>
+        <v>0.73059</v>
       </c>
       <c r="C28" s="0">
         <f>A28*B28</f>
         <v/>
       </c>
       <c r="D28" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E28" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F28" s="0">
         <f>A28*200</f>
@@ -2546,20 +2546,20 @@
     </row>
     <row r="29">
       <c r="A29" s="0" t="n">
-        <v>1.3528395</v>
+        <v>1.3665874</v>
       </c>
       <c r="B29" s="0" t="n">
-        <v>0.72542</v>
+        <v>0.72719</v>
       </c>
       <c r="C29" s="0">
         <f>A29*B29</f>
         <v/>
       </c>
       <c r="D29" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E29" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F29" s="0">
         <f>A29*200</f>
@@ -2620,20 +2620,20 @@
     </row>
     <row r="30">
       <c r="A30" s="0" t="n">
-        <v>1.4037578</v>
+        <v>1.4175059</v>
       </c>
       <c r="B30" s="0" t="n">
-        <v>0.72213</v>
+        <v>0.72372</v>
       </c>
       <c r="C30" s="0">
         <f>A30*B30</f>
         <v/>
       </c>
       <c r="D30" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E30" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F30" s="0">
         <f>A30*200</f>
@@ -2694,20 +2694,20 @@
     </row>
     <row r="31">
       <c r="A31" s="0" t="n">
-        <v>1.454167</v>
+        <v>1.4684241</v>
       </c>
       <c r="B31" s="0" t="n">
-        <v>0.71929</v>
+        <v>0.72078</v>
       </c>
       <c r="C31" s="0">
         <f>A31*B31</f>
         <v/>
       </c>
       <c r="D31" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E31" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F31" s="0">
         <f>A31*200</f>
@@ -2768,20 +2768,20 @@
     </row>
     <row r="32">
       <c r="A32" s="0" t="n">
-        <v>1.5050853</v>
+        <v>1.5193424</v>
       </c>
       <c r="B32" s="0" t="n">
-        <v>0.7156</v>
+        <v>0.71767</v>
       </c>
       <c r="C32" s="0">
         <f>A32*B32</f>
         <v/>
       </c>
       <c r="D32" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E32" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F32" s="0">
         <f>A32*200</f>
@@ -2835,20 +2835,20 @@
     </row>
     <row r="33">
       <c r="A33" s="0" t="n">
-        <v>1.5605862</v>
+        <v>1.5697515</v>
       </c>
       <c r="B33" s="0" t="n">
-        <v>0.71278</v>
+        <v>0.7144</v>
       </c>
       <c r="C33" s="0">
         <f>A33*B33</f>
         <v/>
       </c>
       <c r="D33" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E33" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F33" s="0">
         <f>A33*200</f>
@@ -2902,20 +2902,20 @@
     </row>
     <row r="34">
       <c r="A34" s="0" t="n">
-        <v>1.6120138</v>
+        <v>1.6211791</v>
       </c>
       <c r="B34" s="0" t="n">
-        <v>0.70948</v>
+        <v>0.71154</v>
       </c>
       <c r="C34" s="0">
         <f>A34*B34</f>
         <v/>
       </c>
       <c r="D34" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E34" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F34" s="0">
         <f>A34*200</f>
@@ -2969,20 +2969,20 @@
     </row>
     <row r="35">
       <c r="A35" s="0" t="n">
-        <v>1.662423</v>
+        <v>1.6715881</v>
       </c>
       <c r="B35" s="0" t="n">
-        <v>0.70636</v>
+        <v>0.70852</v>
       </c>
       <c r="C35" s="0">
         <f>A35*B35</f>
         <v/>
       </c>
       <c r="D35" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E35" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F35" s="0">
         <f>A35*200</f>
@@ -3036,20 +3036,20 @@
     </row>
     <row r="36">
       <c r="A36" s="0" t="n">
-        <v>1.7133411</v>
+        <v>1.7230156</v>
       </c>
       <c r="B36" s="0" t="n">
-        <v>0.70344</v>
+        <v>0.70528</v>
       </c>
       <c r="C36" s="0">
         <f>A36*B36</f>
         <v/>
       </c>
       <c r="D36" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E36" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F36" s="0">
         <f>A36*200</f>
@@ -3103,20 +3103,20 @@
     </row>
     <row r="37">
       <c r="A37" s="0" t="n">
-        <v>1.7647687</v>
+        <v>1.7744431</v>
       </c>
       <c r="B37" s="0" t="n">
-        <v>0.7005400000000001</v>
+        <v>0.70228</v>
       </c>
       <c r="C37" s="0">
         <f>A37*B37</f>
         <v/>
       </c>
       <c r="D37" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E37" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F37" s="0">
         <f>A37*200</f>
@@ -3170,20 +3170,20 @@
     </row>
     <row r="38">
       <c r="A38" s="0" t="n">
-        <v>1.8151779</v>
+        <v>1.8253615</v>
       </c>
       <c r="B38" s="0" t="n">
-        <v>0.69756</v>
+        <v>0.69924</v>
       </c>
       <c r="C38" s="0">
         <f>A38*B38</f>
         <v/>
       </c>
       <c r="D38" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E38" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F38" s="0">
         <f>A38*200</f>
@@ -3237,20 +3237,20 @@
     </row>
     <row r="39">
       <c r="A39" s="0" t="n">
-        <v>1.8671146</v>
+        <v>1.8778075</v>
       </c>
       <c r="B39" s="0" t="n">
-        <v>0.6946</v>
+        <v>0.69653</v>
       </c>
       <c r="C39" s="0">
         <f>A39*B39</f>
         <v/>
       </c>
       <c r="D39" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E39" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F39" s="0">
         <f>A39*200</f>
@@ -3304,20 +3304,20 @@
     </row>
     <row r="40">
       <c r="A40" s="0" t="n">
-        <v>1.9175238</v>
+        <v>1.9287257</v>
       </c>
       <c r="B40" s="0" t="n">
-        <v>0.69172</v>
+        <v>0.6938</v>
       </c>
       <c r="C40" s="0">
         <f>A40*B40</f>
         <v/>
       </c>
       <c r="D40" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E40" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F40" s="0">
         <f>A40*200</f>
@@ -3371,20 +3371,20 @@
     </row>
     <row r="41">
       <c r="A41" s="0" t="n">
-        <v>1.9730247</v>
+        <v>1.9791349</v>
       </c>
       <c r="B41" s="0" t="n">
-        <v>0.68876</v>
+        <v>0.69067</v>
       </c>
       <c r="C41" s="0">
         <f>A41*B41</f>
         <v/>
       </c>
       <c r="D41" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E41" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F41" s="0">
         <f>A41*200</f>
@@ -3438,20 +3438,20 @@
     </row>
     <row r="42">
       <c r="A42" s="0" t="n">
-        <v>2.0259799</v>
+        <v>2.0295441</v>
       </c>
       <c r="B42" s="0" t="n">
-        <v>0.68551</v>
+        <v>0.68798</v>
       </c>
       <c r="C42" s="0">
         <f>A42*B42</f>
         <v/>
       </c>
       <c r="D42" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E42" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F42" s="0">
         <f>A42*200</f>
@@ -3505,20 +3505,20 @@
     </row>
     <row r="43">
       <c r="A43" s="0" t="n">
-        <v>2.0784258</v>
+        <v>2.0799534</v>
       </c>
       <c r="B43" s="0" t="n">
-        <v>0.6827800000000001</v>
+        <v>0.68509</v>
       </c>
       <c r="C43" s="0">
         <f>A43*B43</f>
         <v/>
       </c>
       <c r="D43" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E43" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F43" s="0">
         <f>A43*200</f>
@@ -3572,20 +3572,20 @@
     </row>
     <row r="44">
       <c r="A44" s="0" t="n">
-        <v>2.128835</v>
+        <v>2.1339268</v>
       </c>
       <c r="B44" s="0" t="n">
-        <v>0.67994</v>
+        <v>0.68221</v>
       </c>
       <c r="C44" s="0">
         <f>A44*B44</f>
         <v/>
       </c>
       <c r="D44" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E44" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F44" s="0">
         <f>A44*200</f>
@@ -3639,20 +3639,20 @@
     </row>
     <row r="45">
       <c r="A45" s="0" t="n">
-        <v>2.1797532</v>
+        <v>2.1853542</v>
       </c>
       <c r="B45" s="0" t="n">
-        <v>0.67711</v>
+        <v>0.67919</v>
       </c>
       <c r="C45" s="0">
         <f>A45*B45</f>
         <v/>
       </c>
       <c r="D45" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E45" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F45" s="0">
         <f>A45*200</f>
@@ -3706,20 +3706,20 @@
     </row>
     <row r="46">
       <c r="A46" s="0" t="n">
-        <v>2.2311809</v>
+        <v>2.2362725</v>
       </c>
       <c r="B46" s="0" t="n">
-        <v>0.67425</v>
+        <v>0.67685</v>
       </c>
       <c r="C46" s="0">
         <f>A46*B46</f>
         <v/>
       </c>
       <c r="D46" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E46" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F46" s="0">
         <f>A46*200</f>
@@ -3773,20 +3773,20 @@
     </row>
     <row r="47">
       <c r="A47" s="0" t="n">
-        <v>2.2831174</v>
+        <v>2.2897366</v>
       </c>
       <c r="B47" s="0" t="n">
-        <v>0.67144</v>
+        <v>0.674</v>
       </c>
       <c r="C47" s="0">
         <f>A47*B47</f>
         <v/>
       </c>
       <c r="D47" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E47" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F47" s="0">
         <f>A47*200</f>
@@ -3840,20 +3840,20 @@
     </row>
     <row r="48">
       <c r="A48" s="0" t="n">
-        <v>2.3335266</v>
+        <v>2.340146</v>
       </c>
       <c r="B48" s="0" t="n">
-        <v>0.66881</v>
+        <v>0.67131</v>
       </c>
       <c r="C48" s="0">
         <f>A48*B48</f>
         <v/>
       </c>
       <c r="D48" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E48" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F48" s="0">
         <f>A48*200</f>
@@ -3907,20 +3907,20 @@
     </row>
     <row r="49">
       <c r="A49" s="0" t="n">
-        <v>2.3839358</v>
+        <v>2.3905552</v>
       </c>
       <c r="B49" s="0" t="n">
-        <v>0.66604</v>
+        <v>0.6684600000000001</v>
       </c>
       <c r="C49" s="0">
         <f>A49*B49</f>
         <v/>
       </c>
       <c r="D49" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E49" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F49" s="0">
         <f>A49*200</f>
@@ -3974,20 +3974,20 @@
     </row>
     <row r="50">
       <c r="A50" s="0" t="n">
-        <v>2.434854</v>
+        <v>2.4414734</v>
       </c>
       <c r="B50" s="0" t="n">
-        <v>0.6635</v>
+        <v>0.66579</v>
       </c>
       <c r="C50" s="0">
         <f>A50*B50</f>
         <v/>
       </c>
       <c r="D50" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E50" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F50" s="0">
         <f>A50*200</f>
@@ -4041,20 +4041,20 @@
     </row>
     <row r="51">
       <c r="A51" s="0" t="n">
-        <v>2.4867908</v>
+        <v>2.4918826</v>
       </c>
       <c r="B51" s="0" t="n">
-        <v>0.66077</v>
+        <v>0.6631899999999999</v>
       </c>
       <c r="C51" s="0">
         <f>A51*B51</f>
         <v/>
       </c>
       <c r="D51" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E51" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F51" s="0">
         <f>A51*200</f>
@@ -4108,20 +4108,20 @@
     </row>
     <row r="52">
       <c r="A52" s="0" t="n">
-        <v>2.5382183</v>
+        <v>2.542801</v>
       </c>
       <c r="B52" s="0" t="n">
-        <v>0.65813</v>
+        <v>0.66045</v>
       </c>
       <c r="C52" s="0">
         <f>A52*B52</f>
         <v/>
       </c>
       <c r="D52" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E52" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F52" s="0">
         <f>A52*200</f>
@@ -4175,20 +4175,20 @@
     </row>
     <row r="53">
       <c r="A53" s="0" t="n">
-        <v>2.5901548</v>
+        <v>2.5932102</v>
       </c>
       <c r="B53" s="0" t="n">
-        <v>0.65539</v>
+        <v>0.65787</v>
       </c>
       <c r="C53" s="0">
         <f>A53*B53</f>
         <v/>
       </c>
       <c r="D53" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E53" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F53" s="0">
         <f>A53*200</f>
@@ -4242,20 +4242,20 @@
     </row>
     <row r="54">
       <c r="A54" s="0" t="n">
-        <v>2.6415823</v>
+        <v>2.646165</v>
       </c>
       <c r="B54" s="0" t="n">
-        <v>0.65281</v>
+        <v>0.65525</v>
       </c>
       <c r="C54" s="0">
         <f>A54*B54</f>
         <v/>
       </c>
       <c r="D54" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E54" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F54" s="0">
         <f>A54*200</f>
@@ -4309,20 +4309,20 @@
     </row>
     <row r="55">
       <c r="A55" s="0" t="n">
-        <v>2.6919915</v>
+        <v>2.6970835</v>
       </c>
       <c r="B55" s="0" t="n">
-        <v>0.65029</v>
+        <v>0.65287</v>
       </c>
       <c r="C55" s="0">
         <f>A55*B55</f>
         <v/>
       </c>
       <c r="D55" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E55" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F55" s="0">
         <f>A55*200</f>
@@ -4376,20 +4376,20 @@
     </row>
     <row r="56">
       <c r="A56" s="0" t="n">
-        <v>2.7424006</v>
+        <v>2.7474927</v>
       </c>
       <c r="B56" s="0" t="n">
-        <v>0.64784</v>
+        <v>0.65002</v>
       </c>
       <c r="C56" s="0">
         <f>A56*B56</f>
         <v/>
       </c>
       <c r="D56" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E56" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F56" s="0">
         <f>A56*200</f>
@@ -4443,20 +4443,20 @@
     </row>
     <row r="57">
       <c r="A57" s="0" t="n">
-        <v>2.7933191</v>
+        <v>2.7999385</v>
       </c>
       <c r="B57" s="0" t="n">
-        <v>0.6450900000000001</v>
+        <v>0.64725</v>
       </c>
       <c r="C57" s="0">
         <f>A57*B57</f>
         <v/>
       </c>
       <c r="D57" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E57" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F57" s="0">
         <f>A57*200</f>
@@ -4510,20 +4510,20 @@
     </row>
     <row r="58">
       <c r="A58" s="0" t="n">
-        <v>2.8472925</v>
+        <v>2.8508567</v>
       </c>
       <c r="B58" s="0" t="n">
-        <v>0.64257</v>
+        <v>0.64494</v>
       </c>
       <c r="C58" s="0">
         <f>A58*B58</f>
         <v/>
       </c>
       <c r="D58" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E58" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F58" s="0">
         <f>A58*200</f>
@@ -4577,20 +4577,20 @@
     </row>
     <row r="59">
       <c r="A59" s="0" t="n">
-        <v>2.8977017</v>
+        <v>2.904321</v>
       </c>
       <c r="B59" s="0" t="n">
-        <v>0.63984</v>
+        <v>0.64215</v>
       </c>
       <c r="C59" s="0">
         <f>A59*B59</f>
         <v/>
       </c>
       <c r="D59" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E59" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F59" s="0">
         <f>A59*200</f>
@@ -4644,20 +4644,20 @@
     </row>
     <row r="60">
       <c r="A60" s="0" t="n">
-        <v>2.9481108</v>
+        <v>2.9567668</v>
       </c>
       <c r="B60" s="0" t="n">
-        <v>0.63746</v>
+        <v>0.63942</v>
       </c>
       <c r="C60" s="0">
         <f>A60*B60</f>
         <v/>
       </c>
       <c r="D60" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E60" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F60" s="0">
         <f>A60*200</f>
@@ -4711,20 +4711,20 @@
     </row>
     <row r="61">
       <c r="A61" s="0" t="n">
-        <v>3.001575</v>
+        <v>3.0076851</v>
       </c>
       <c r="B61" s="0" t="n">
-        <v>0.63484</v>
+        <v>0.6369</v>
       </c>
       <c r="C61" s="0">
         <f>A61*B61</f>
         <v/>
       </c>
       <c r="D61" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E61" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F61" s="0">
         <f>A61*200</f>
@@ -4778,20 +4778,20 @@
     </row>
     <row r="62">
       <c r="A62" s="0" t="n">
-        <v>3.0530024</v>
+        <v>3.0611492</v>
       </c>
       <c r="B62" s="0" t="n">
-        <v>0.6323800000000001</v>
+        <v>0.63448</v>
       </c>
       <c r="C62" s="0">
         <f>A62*B62</f>
         <v/>
       </c>
       <c r="D62" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E62" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F62" s="0">
         <f>A62*200</f>
@@ -4845,20 +4845,20 @@
     </row>
     <row r="63">
       <c r="A63" s="0" t="n">
-        <v>3.1039207</v>
+        <v>3.1115586</v>
       </c>
       <c r="B63" s="0" t="n">
-        <v>0.63007</v>
+        <v>0.6317700000000001</v>
       </c>
       <c r="C63" s="0">
         <f>A63*B63</f>
         <v/>
       </c>
       <c r="D63" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E63" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F63" s="0">
         <f>A63*200</f>
@@ -4912,20 +4912,20 @@
     </row>
     <row r="64">
       <c r="A64" s="0" t="n">
-        <v>3.1553481</v>
+        <v>3.1665503</v>
       </c>
       <c r="B64" s="0" t="n">
-        <v>0.62715</v>
+        <v>0.62898</v>
       </c>
       <c r="C64" s="0">
         <f>A64*B64</f>
         <v/>
       </c>
       <c r="D64" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E64" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F64" s="0">
         <f>A64*200</f>
@@ -4979,20 +4979,20 @@
     </row>
     <row r="65">
       <c r="A65" s="0" t="n">
-        <v>3.2072849</v>
+        <v>3.2184868</v>
       </c>
       <c r="B65" s="0" t="n">
-        <v>0.6248</v>
+        <v>0.6264999999999999</v>
       </c>
       <c r="C65" s="0">
         <f>A65*B65</f>
         <v/>
       </c>
       <c r="D65" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E65" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F65" s="0">
         <f>A65*200</f>
@@ -5046,20 +5046,20 @@
     </row>
     <row r="66">
       <c r="A66" s="0" t="n">
-        <v>3.26024</v>
+        <v>3.2724604</v>
       </c>
       <c r="B66" s="0" t="n">
-        <v>0.62214</v>
+        <v>0.624</v>
       </c>
       <c r="C66" s="0">
         <f>A66*B66</f>
         <v/>
       </c>
       <c r="D66" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E66" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F66" s="0">
         <f>A66*200</f>
@@ -5113,20 +5113,20 @@
     </row>
     <row r="67">
       <c r="A67" s="0" t="n">
-        <v>3.3126858</v>
+        <v>3.3238877</v>
       </c>
       <c r="B67" s="0" t="n">
-        <v>0.61961</v>
+        <v>0.62155</v>
       </c>
       <c r="C67" s="0">
         <f>A67*B67</f>
         <v/>
       </c>
       <c r="D67" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E67" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F67" s="0">
         <f>A67*200</f>
@@ -5180,20 +5180,20 @@
     </row>
     <row r="68">
       <c r="A68" s="0" t="n">
-        <v>3.363604</v>
+        <v>3.3742969</v>
       </c>
       <c r="B68" s="0" t="n">
-        <v>0.6172</v>
+        <v>0.6186700000000001</v>
       </c>
       <c r="C68" s="0">
         <f>A68*B68</f>
         <v/>
       </c>
       <c r="D68" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E68" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F68" s="0">
         <f>A68*200</f>
@@ -5247,20 +5247,20 @@
     </row>
     <row r="69">
       <c r="A69" s="0" t="n">
-        <v>3.4150317</v>
+        <v>3.4252156</v>
       </c>
       <c r="B69" s="0" t="n">
-        <v>0.61489</v>
+        <v>0.6163999999999999</v>
       </c>
       <c r="C69" s="0">
         <f>A69*B69</f>
         <v/>
       </c>
       <c r="D69" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E69" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F69" s="0">
         <f>A69*200</f>
@@ -5314,20 +5314,20 @@
     </row>
     <row r="70">
       <c r="A70" s="0" t="n">
-        <v>3.46595</v>
+        <v>3.4766428</v>
       </c>
       <c r="B70" s="0" t="n">
-        <v>0.6123499999999999</v>
+        <v>0.61399</v>
       </c>
       <c r="C70" s="0">
         <f>A70*B70</f>
         <v/>
       </c>
       <c r="D70" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E70" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F70" s="0">
         <f>A70*200</f>
@@ -5381,20 +5381,20 @@
     </row>
     <row r="71">
       <c r="A71" s="0" t="n">
-        <v>3.5168684</v>
+        <v>3.5275613</v>
       </c>
       <c r="B71" s="0" t="n">
-        <v>0.60994</v>
+        <v>0.6112</v>
       </c>
       <c r="C71" s="0">
         <f>A71*B71</f>
         <v/>
       </c>
       <c r="D71" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E71" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F71" s="0">
         <f>A71*200</f>
@@ -5448,20 +5448,20 @@
     </row>
     <row r="72">
       <c r="A72" s="0" t="n">
-        <v>3.5713511</v>
+        <v>3.5784797</v>
       </c>
       <c r="B72" s="0" t="n">
-        <v>0.60748</v>
+        <v>0.60889</v>
       </c>
       <c r="C72" s="0">
         <f>A72*B72</f>
         <v/>
       </c>
       <c r="D72" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E72" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F72" s="0">
         <f>A72*200</f>
@@ -5515,20 +5515,20 @@
     </row>
     <row r="73">
       <c r="A73" s="0" t="n">
-        <v>3.6237971</v>
+        <v>3.6293979</v>
       </c>
       <c r="B73" s="0" t="n">
-        <v>0.60506</v>
+        <v>0.60647</v>
       </c>
       <c r="C73" s="0">
         <f>A73*B73</f>
         <v/>
       </c>
       <c r="D73" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E73" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F73" s="0">
         <f>A73*200</f>
@@ -5582,20 +5582,20 @@
     </row>
     <row r="74">
       <c r="A74" s="0" t="n">
-        <v>3.6782793</v>
+        <v>3.6843896</v>
       </c>
       <c r="B74" s="0" t="n">
-        <v>0.60244</v>
+        <v>0.60397</v>
       </c>
       <c r="C74" s="0">
         <f>A74*B74</f>
         <v/>
       </c>
       <c r="D74" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E74" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F74" s="0">
         <f>A74*200</f>
@@ -5649,20 +5649,20 @@
     </row>
     <row r="75">
       <c r="A75" s="0" t="n">
-        <v>3.729707</v>
+        <v>3.737854</v>
       </c>
       <c r="B75" s="0" t="n">
-        <v>0.59984</v>
+        <v>0.60139</v>
       </c>
       <c r="C75" s="0">
         <f>A75*B75</f>
         <v/>
       </c>
       <c r="D75" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E75" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F75" s="0">
         <f>A75*200</f>
@@ -5716,20 +5716,20 @@
     </row>
     <row r="76">
       <c r="A76" s="0" t="n">
-        <v>3.7811345</v>
+        <v>3.7923364</v>
       </c>
       <c r="B76" s="0" t="n">
-        <v>0.59761</v>
+        <v>0.59885</v>
       </c>
       <c r="C76" s="0">
         <f>A76*B76</f>
         <v/>
       </c>
       <c r="D76" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E76" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F76" s="0">
         <f>A76*200</f>
@@ -5783,20 +5783,20 @@
     </row>
     <row r="77">
       <c r="A77" s="0" t="n">
-        <v>3.8315437</v>
+        <v>3.8427458</v>
       </c>
       <c r="B77" s="0" t="n">
-        <v>0.59534</v>
+        <v>0.59629</v>
       </c>
       <c r="C77" s="0">
         <f>A77*B77</f>
         <v/>
       </c>
       <c r="D77" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E77" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F77" s="0">
         <f>A77*200</f>
@@ -5850,20 +5850,20 @@
     </row>
     <row r="78">
       <c r="A78" s="0" t="n">
-        <v>3.8829709</v>
+        <v>3.89621</v>
       </c>
       <c r="B78" s="0" t="n">
-        <v>0.5931</v>
+        <v>0.59394</v>
       </c>
       <c r="C78" s="0">
         <f>A78*B78</f>
         <v/>
       </c>
       <c r="D78" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E78" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F78" s="0">
         <f>A78*200</f>
@@ -5917,20 +5917,20 @@
     </row>
     <row r="79">
       <c r="A79" s="0" t="n">
-        <v>3.9349077</v>
+        <v>3.9476375</v>
       </c>
       <c r="B79" s="0" t="n">
-        <v>0.59062</v>
+        <v>0.5915</v>
       </c>
       <c r="C79" s="0">
         <f>A79*B79</f>
         <v/>
       </c>
       <c r="D79" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E79" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F79" s="0">
         <f>A79*200</f>
@@ -5984,20 +5984,20 @@
     </row>
     <row r="80">
       <c r="A80" s="0" t="n">
-        <v>3.9888816</v>
+        <v>4.0005923</v>
       </c>
       <c r="B80" s="0" t="n">
-        <v>0.58831</v>
+        <v>0.58908</v>
       </c>
       <c r="C80" s="0">
         <f>A80*B80</f>
         <v/>
       </c>
       <c r="D80" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E80" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F80" s="0">
         <f>A80*200</f>
@@ -6051,20 +6051,20 @@
     </row>
     <row r="81">
       <c r="A81" s="0" t="n">
-        <v>4.0418364</v>
+        <v>4.0540566</v>
       </c>
       <c r="B81" s="0" t="n">
-        <v>0.58583</v>
+        <v>0.58652</v>
       </c>
       <c r="C81" s="0">
         <f>A81*B81</f>
         <v/>
       </c>
       <c r="D81" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E81" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F81" s="0">
         <f>A81*200</f>
@@ -6118,20 +6118,20 @@
     </row>
     <row r="82">
       <c r="A82" s="0" t="n">
-        <v>4.0922456</v>
+        <v>4.1059937</v>
       </c>
       <c r="B82" s="0" t="n">
-        <v>0.58346</v>
+        <v>0.58396</v>
       </c>
       <c r="C82" s="0">
         <f>A82*B82</f>
         <v/>
       </c>
       <c r="D82" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E82" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F82" s="0">
         <f>A82*200</f>
@@ -6185,20 +6185,20 @@
     </row>
     <row r="83">
       <c r="A83" s="0" t="n">
-        <v>4.1431641</v>
+        <v>4.1584395</v>
       </c>
       <c r="B83" s="0" t="n">
-        <v>0.58096</v>
+        <v>0.5815</v>
       </c>
       <c r="C83" s="0">
         <f>A83*B83</f>
         <v/>
       </c>
       <c r="D83" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E83" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F83" s="0">
         <f>A83*200</f>
@@ -6252,20 +6252,20 @@
     </row>
     <row r="84">
       <c r="A84" s="0" t="n">
-        <v>4.1961191</v>
+        <v>4.2113945</v>
       </c>
       <c r="B84" s="0" t="n">
-        <v>0.57877</v>
+        <v>0.57903</v>
       </c>
       <c r="C84" s="0">
         <f>A84*B84</f>
         <v/>
       </c>
       <c r="D84" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E84" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F84" s="0">
         <f>A84*200</f>
@@ -6319,20 +6319,20 @@
     </row>
     <row r="85">
       <c r="A85" s="0" t="n">
-        <v>4.2485649</v>
+        <v>4.2628218</v>
       </c>
       <c r="B85" s="0" t="n">
-        <v>0.57667</v>
+        <v>0.57655</v>
       </c>
       <c r="C85" s="0">
         <f>A85*B85</f>
         <v/>
       </c>
       <c r="D85" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E85" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F85" s="0">
         <f>A85*200</f>
@@ -6386,20 +6386,20 @@
     </row>
     <row r="86">
       <c r="A86" s="0" t="n">
-        <v>4.3025381</v>
+        <v>4.313231</v>
       </c>
       <c r="B86" s="0" t="n">
-        <v>0.5742</v>
+        <v>0.57441</v>
       </c>
       <c r="C86" s="0">
         <f>A86*B86</f>
         <v/>
       </c>
       <c r="D86" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E86" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F86" s="0">
         <f>A86*200</f>
@@ -6453,20 +6453,20 @@
     </row>
     <row r="87">
       <c r="A87" s="0" t="n">
-        <v>4.353457</v>
+        <v>4.3656772</v>
       </c>
       <c r="B87" s="0" t="n">
-        <v>0.5718</v>
+        <v>0.57212</v>
       </c>
       <c r="C87" s="0">
         <f>A87*B87</f>
         <v/>
       </c>
       <c r="D87" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E87" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F87" s="0">
         <f>A87*200</f>
@@ -6520,20 +6520,20 @@
     </row>
     <row r="88">
       <c r="A88" s="0" t="n">
-        <v>4.4038662</v>
+        <v>4.4171045</v>
       </c>
       <c r="B88" s="0" t="n">
-        <v>0.56958</v>
+        <v>0.56962</v>
       </c>
       <c r="C88" s="0">
         <f>A88*B88</f>
         <v/>
       </c>
       <c r="D88" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E88" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F88" s="0">
         <f>A88*200</f>
@@ -6587,20 +6587,20 @@
     </row>
     <row r="89">
       <c r="A89" s="0" t="n">
-        <v>4.4542754</v>
+        <v>4.469041</v>
       </c>
       <c r="B89" s="0" t="n">
-        <v>0.56729</v>
+        <v>0.56716</v>
       </c>
       <c r="C89" s="0">
         <f>A89*B89</f>
         <v/>
       </c>
       <c r="D89" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E89" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F89" s="0">
         <f>A89*200</f>
@@ -6654,20 +6654,20 @@
     </row>
     <row r="90">
       <c r="A90" s="0" t="n">
-        <v>4.5057026</v>
+        <v>4.5214873</v>
       </c>
       <c r="B90" s="0" t="n">
-        <v>0.56494</v>
+        <v>0.56487</v>
       </c>
       <c r="C90" s="0">
         <f>A90*B90</f>
         <v/>
       </c>
       <c r="D90" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E90" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F90" s="0">
         <f>A90*200</f>
@@ -6721,20 +6721,20 @@
     </row>
     <row r="91">
       <c r="A91" s="0" t="n">
-        <v>4.5561118</v>
+        <v>4.5718965</v>
       </c>
       <c r="B91" s="0" t="n">
-        <v>0.56277</v>
+        <v>0.56248</v>
       </c>
       <c r="C91" s="0">
         <f>A91*B91</f>
         <v/>
       </c>
       <c r="D91" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E91" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F91" s="0">
         <f>A91*200</f>
@@ -6788,20 +6788,20 @@
     </row>
     <row r="92">
       <c r="A92" s="0" t="n">
-        <v>4.6075391</v>
+        <v>4.6233237</v>
       </c>
       <c r="B92" s="0" t="n">
-        <v>0.56042</v>
+        <v>0.56005</v>
       </c>
       <c r="C92" s="0">
         <f>A92*B92</f>
         <v/>
       </c>
       <c r="D92" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E92" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F92" s="0">
         <f>A92*200</f>
@@ -6855,20 +6855,20 @@
     </row>
     <row r="93">
       <c r="A93" s="0" t="n">
-        <v>4.6589668</v>
+        <v>4.6737329</v>
       </c>
       <c r="B93" s="0" t="n">
-        <v>0.55816</v>
+        <v>0.5579499999999999</v>
       </c>
       <c r="C93" s="0">
         <f>A93*B93</f>
         <v/>
       </c>
       <c r="D93" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E93" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F93" s="0">
         <f>A93*200</f>
@@ -6922,20 +6922,20 @@
     </row>
     <row r="94">
       <c r="A94" s="0" t="n">
-        <v>4.7124312</v>
+        <v>4.7287251</v>
       </c>
       <c r="B94" s="0" t="n">
-        <v>0.55614</v>
+        <v>0.55538</v>
       </c>
       <c r="C94" s="0">
         <f>A94*B94</f>
         <v/>
       </c>
       <c r="D94" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E94" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F94" s="0">
         <f>A94*200</f>
@@ -6989,20 +6989,20 @@
     </row>
     <row r="95">
       <c r="A95" s="0" t="n">
-        <v>4.7628403</v>
+        <v>4.7791343</v>
       </c>
       <c r="B95" s="0" t="n">
-        <v>0.5536799999999999</v>
+        <v>0.55305</v>
       </c>
       <c r="C95" s="0">
         <f>A95*B95</f>
         <v/>
       </c>
       <c r="D95" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E95" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F95" s="0">
         <f>A95*200</f>
@@ -7056,20 +7056,20 @@
     </row>
     <row r="96">
       <c r="A96" s="0" t="n">
-        <v>4.8132495</v>
+        <v>4.829543</v>
       </c>
       <c r="B96" s="0" t="n">
-        <v>0.5515600000000001</v>
+        <v>0.5507</v>
       </c>
       <c r="C96" s="0">
         <f>A96*B96</f>
         <v/>
       </c>
       <c r="D96" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E96" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F96" s="0">
         <f>A96*200</f>
@@ -7123,20 +7123,20 @@
     </row>
     <row r="97">
       <c r="A97" s="0" t="n">
-        <v>4.8641675</v>
+        <v>4.8799521</v>
       </c>
       <c r="B97" s="0" t="n">
-        <v>0.5493400000000001</v>
+        <v>0.54843</v>
       </c>
       <c r="C97" s="0">
         <f>A97*B97</f>
         <v/>
       </c>
       <c r="D97" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E97" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F97" s="0">
         <f>A97*200</f>
@@ -7190,20 +7190,20 @@
     </row>
     <row r="98">
       <c r="A98" s="0" t="n">
-        <v>4.9145767</v>
+        <v>4.9313799</v>
       </c>
       <c r="B98" s="0" t="n">
-        <v>0.54701</v>
+        <v>0.54606</v>
       </c>
       <c r="C98" s="0">
         <f>A98*B98</f>
         <v/>
       </c>
       <c r="D98" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E98" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F98" s="0">
         <f>A98*200</f>
@@ -7257,20 +7257,20 @@
     </row>
     <row r="99">
       <c r="A99" s="0" t="n">
-        <v>4.9685503</v>
+        <v>4.9817891</v>
       </c>
       <c r="B99" s="0" t="n">
-        <v>0.54484</v>
+        <v>0.54392</v>
       </c>
       <c r="C99" s="0">
         <f>A99*B99</f>
         <v/>
       </c>
       <c r="D99" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E99" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F99" s="0">
         <f>A99*200</f>
@@ -7324,20 +7324,20 @@
     </row>
     <row r="100">
       <c r="A100" s="0" t="n">
-        <v>5.0209961</v>
+        <v>5.0372896</v>
       </c>
       <c r="B100" s="0" t="n">
-        <v>0.54236</v>
+        <v>0.54142</v>
       </c>
       <c r="C100" s="0">
         <f>A100*B100</f>
         <v/>
       </c>
       <c r="D100" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E100" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F100" s="0">
         <f>A100*200</f>
@@ -7391,20 +7391,20 @@
     </row>
     <row r="101">
       <c r="A101" s="0" t="n">
-        <v>5.0719146</v>
+        <v>5.0897358</v>
       </c>
       <c r="B101" s="0" t="n">
-        <v>0.54022</v>
+        <v>0.53894</v>
       </c>
       <c r="C101" s="0">
         <f>A101*B101</f>
         <v/>
       </c>
       <c r="D101" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E101" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F101" s="0">
         <f>A101*200</f>
@@ -7458,20 +7458,20 @@
     </row>
     <row r="102">
       <c r="A102" s="0" t="n">
-        <v>5.1248696</v>
+        <v>5.1411631</v>
       </c>
       <c r="B102" s="0" t="n">
-        <v>0.53816</v>
+        <v>0.53678</v>
       </c>
       <c r="C102" s="0">
         <f>A102*B102</f>
         <v/>
       </c>
       <c r="D102" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E102" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F102" s="0">
         <f>A102*200</f>
@@ -7525,20 +7525,20 @@
     </row>
     <row r="103">
       <c r="A103" s="0" t="n">
-        <v>5.1752783</v>
+        <v>5.1920815</v>
       </c>
       <c r="B103" s="0" t="n">
-        <v>0.53581</v>
+        <v>0.53445</v>
       </c>
       <c r="C103" s="0">
         <f>A103*B103</f>
         <v/>
       </c>
       <c r="D103" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E103" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F103" s="0">
         <f>A103*200</f>
@@ -7592,20 +7592,20 @@
     </row>
     <row r="104">
       <c r="A104" s="0" t="n">
-        <v>5.2307793</v>
+        <v>5.2435093</v>
       </c>
       <c r="B104" s="0" t="n">
-        <v>0.53338</v>
+        <v>0.53229</v>
       </c>
       <c r="C104" s="0">
         <f>A104*B104</f>
         <v/>
       </c>
       <c r="D104" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E104" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F104" s="0">
         <f>A104*200</f>
@@ -7659,20 +7659,20 @@
     </row>
     <row r="105">
       <c r="A105" s="0" t="n">
-        <v>5.281189</v>
+        <v>5.2990098</v>
       </c>
       <c r="B105" s="0" t="n">
-        <v>0.53142</v>
+        <v>0.52983</v>
       </c>
       <c r="C105" s="0">
         <f>A105*B105</f>
         <v/>
       </c>
       <c r="D105" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E105" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F105" s="0">
         <f>A105*200</f>
@@ -7726,20 +7726,20 @@
     </row>
     <row r="106">
       <c r="A106" s="0" t="n">
-        <v>5.3321064</v>
+        <v>5.3509473</v>
       </c>
       <c r="B106" s="0" t="n">
-        <v>0.52907</v>
+        <v>0.52733</v>
       </c>
       <c r="C106" s="0">
         <f>A106*B106</f>
         <v/>
       </c>
       <c r="D106" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E106" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F106" s="0">
         <f>A106*200</f>
@@ -7793,20 +7793,20 @@
     </row>
     <row r="107">
       <c r="A107" s="0" t="n">
-        <v>5.3845527</v>
+        <v>5.402374</v>
       </c>
       <c r="B107" s="0" t="n">
-        <v>0.52701</v>
+        <v>0.52489</v>
       </c>
       <c r="C107" s="0">
         <f>A107*B107</f>
         <v/>
       </c>
       <c r="D107" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E107" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F107" s="0">
         <f>A107*200</f>
@@ -7860,20 +7860,20 @@
     </row>
     <row r="108">
       <c r="A108" s="0" t="n">
-        <v>5.4375078</v>
+        <v>5.4548198</v>
       </c>
       <c r="B108" s="0" t="n">
-        <v>0.52481</v>
+        <v>0.52271</v>
       </c>
       <c r="C108" s="0">
         <f>A108*B108</f>
         <v/>
       </c>
       <c r="D108" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E108" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F108" s="0">
         <f>A108*200</f>
@@ -7927,20 +7927,20 @@
     </row>
     <row r="109">
       <c r="A109" s="0" t="n">
-        <v>5.4879165</v>
+        <v>5.5062476</v>
       </c>
       <c r="B109" s="0" t="n">
-        <v>0.52242</v>
+        <v>0.52059</v>
       </c>
       <c r="C109" s="0">
         <f>A109*B109</f>
         <v/>
       </c>
       <c r="D109" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E109" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F109" s="0">
         <f>A109*200</f>
@@ -7994,20 +7994,20 @@
     </row>
     <row r="110">
       <c r="A110" s="0" t="n">
-        <v>5.5408721</v>
+        <v>5.5586938</v>
       </c>
       <c r="B110" s="0" t="n">
-        <v>0.52038</v>
+        <v>0.51818</v>
       </c>
       <c r="C110" s="0">
         <f>A110*B110</f>
         <v/>
       </c>
       <c r="D110" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E110" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F110" s="0">
         <f>A110*200</f>
@@ -8061,20 +8061,20 @@
     </row>
     <row r="111">
       <c r="A111" s="0" t="n">
-        <v>5.5917905</v>
+        <v>5.6091025</v>
       </c>
       <c r="B111" s="0" t="n">
-        <v>0.51813</v>
+        <v>0.51597</v>
       </c>
       <c r="C111" s="0">
         <f>A111*B111</f>
         <v/>
       </c>
       <c r="D111" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E111" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F111" s="0">
         <f>A111*200</f>
@@ -8128,20 +8128,20 @@
     </row>
     <row r="112">
       <c r="A112" s="0" t="n">
-        <v>5.642709</v>
+        <v>5.6610396</v>
       </c>
       <c r="B112" s="0" t="n">
-        <v>0.51614</v>
+        <v>0.51362</v>
       </c>
       <c r="C112" s="0">
         <f>A112*B112</f>
         <v/>
       </c>
       <c r="D112" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E112" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F112" s="0">
         <f>A112*200</f>
@@ -8195,20 +8195,20 @@
     </row>
     <row r="113">
       <c r="A113" s="0" t="n">
-        <v>5.6941362</v>
+        <v>5.7129761</v>
       </c>
       <c r="B113" s="0" t="n">
-        <v>0.5137</v>
+        <v>0.51129</v>
       </c>
       <c r="C113" s="0">
         <f>A113*B113</f>
         <v/>
       </c>
       <c r="D113" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E113" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F113" s="0">
         <f>A113*200</f>
@@ -8262,20 +8262,20 @@
     </row>
     <row r="114">
       <c r="A114" s="0" t="n">
-        <v>5.7445449</v>
+        <v>5.7674585</v>
       </c>
       <c r="B114" s="0" t="n">
-        <v>0.5116000000000001</v>
+        <v>0.5089399999999999</v>
       </c>
       <c r="C114" s="0">
         <f>A114*B114</f>
         <v/>
       </c>
       <c r="D114" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E114" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F114" s="0">
         <f>A114*200</f>
@@ -8329,20 +8329,20 @@
     </row>
     <row r="115">
       <c r="A115" s="0" t="n">
-        <v>5.7949546</v>
+        <v>5.8183774</v>
       </c>
       <c r="B115" s="0" t="n">
-        <v>0.50929</v>
+        <v>0.50654</v>
       </c>
       <c r="C115" s="0">
         <f>A115*B115</f>
         <v/>
       </c>
       <c r="D115" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E115" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F115" s="0">
         <f>A115*200</f>
@@ -8396,20 +8396,20 @@
     </row>
     <row r="116">
       <c r="A116" s="0" t="n">
-        <v>5.845873</v>
+        <v>5.8698042</v>
       </c>
       <c r="B116" s="0" t="n">
-        <v>0.50745</v>
+        <v>0.5047</v>
       </c>
       <c r="C116" s="0">
         <f>A116*B116</f>
         <v/>
       </c>
       <c r="D116" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E116" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F116" s="0">
         <f>A116*200</f>
@@ -8463,20 +8463,20 @@
     </row>
     <row r="117">
       <c r="A117" s="0" t="n">
-        <v>5.8973003</v>
+        <v>5.9202139</v>
       </c>
       <c r="B117" s="0" t="n">
-        <v>0.50507</v>
+        <v>0.50207</v>
       </c>
       <c r="C117" s="0">
         <f>A117*B117</f>
         <v/>
       </c>
       <c r="D117" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E117" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F117" s="0">
         <f>A117*200</f>
@@ -8530,20 +8530,20 @@
     </row>
     <row r="118">
       <c r="A118" s="0" t="n">
-        <v>5.9482188</v>
+        <v>5.9706226</v>
       </c>
       <c r="B118" s="0" t="n">
-        <v>0.50306</v>
+        <v>0.49995</v>
       </c>
       <c r="C118" s="0">
         <f>A118*B118</f>
         <v/>
       </c>
       <c r="D118" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E118" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F118" s="0">
         <f>A118*200</f>
@@ -8597,20 +8597,20 @@
     </row>
     <row r="119">
       <c r="A119" s="0" t="n">
-        <v>6.0011733</v>
+        <v>6.0225596</v>
       </c>
       <c r="B119" s="0" t="n">
-        <v>0.50073</v>
+        <v>0.49758</v>
       </c>
       <c r="C119" s="0">
         <f>A119*B119</f>
         <v/>
       </c>
       <c r="D119" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E119" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F119" s="0">
         <f>A119*200</f>
@@ -8664,20 +8664,20 @@
     </row>
     <row r="120">
       <c r="A120" s="0" t="n">
-        <v>6.0551475</v>
+        <v>6.0760239</v>
       </c>
       <c r="B120" s="0" t="n">
-        <v>0.49863</v>
+        <v>0.49529</v>
       </c>
       <c r="C120" s="0">
         <f>A120*B120</f>
         <v/>
       </c>
       <c r="D120" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E120" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F120" s="0">
         <f>A120*200</f>
@@ -8731,20 +8731,20 @@
     </row>
     <row r="121">
       <c r="A121" s="0" t="n">
-        <v>6.1055566</v>
+        <v>6.1264326</v>
       </c>
       <c r="B121" s="0" t="n">
-        <v>0.49646</v>
+        <v>0.49296</v>
       </c>
       <c r="C121" s="0">
         <f>A121*B121</f>
         <v/>
       </c>
       <c r="D121" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E121" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F121" s="0">
         <f>A121*200</f>
@@ -8798,20 +8798,20 @@
     </row>
     <row r="122">
       <c r="A122" s="0" t="n">
-        <v>6.1574932</v>
+        <v>6.1793877</v>
       </c>
       <c r="B122" s="0" t="n">
-        <v>0.49451</v>
+        <v>0.49052</v>
       </c>
       <c r="C122" s="0">
         <f>A122*B122</f>
         <v/>
       </c>
       <c r="D122" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E122" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F122" s="0">
         <f>A122*200</f>
@@ -8865,20 +8865,20 @@
     </row>
     <row r="123">
       <c r="A123" s="0" t="n">
-        <v>6.209939</v>
+        <v>6.231834</v>
       </c>
       <c r="B123" s="0" t="n">
-        <v>0.4921</v>
+        <v>0.48857</v>
       </c>
       <c r="C123" s="0">
         <f>A123*B123</f>
         <v/>
       </c>
       <c r="D123" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E123" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F123" s="0">
         <f>A123*200</f>
@@ -8932,20 +8932,20 @@
     </row>
     <row r="124">
       <c r="A124" s="0" t="n">
-        <v>6.2608564</v>
+        <v>6.2832612</v>
       </c>
       <c r="B124" s="0" t="n">
-        <v>0.48974</v>
+        <v>0.48599</v>
       </c>
       <c r="C124" s="0">
         <f>A124*B124</f>
         <v/>
       </c>
       <c r="D124" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E124" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F124" s="0">
         <f>A124*200</f>
@@ -8999,20 +8999,20 @@
     </row>
     <row r="125">
       <c r="A125" s="0" t="n">
-        <v>6.3117749</v>
+        <v>6.3372339</v>
       </c>
       <c r="B125" s="0" t="n">
-        <v>0.48775</v>
+        <v>0.48376</v>
       </c>
       <c r="C125" s="0">
         <f>A125*B125</f>
         <v/>
       </c>
       <c r="D125" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E125" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F125" s="0">
         <f>A125*200</f>
@@ -9066,20 +9066,20 @@
     </row>
     <row r="126">
       <c r="A126" s="0" t="n">
-        <v>6.3626943</v>
+        <v>6.3876436</v>
       </c>
       <c r="B126" s="0" t="n">
-        <v>0.48552</v>
+        <v>0.48149</v>
       </c>
       <c r="C126" s="0">
         <f>A126*B126</f>
         <v/>
       </c>
       <c r="D126" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E126" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F126" s="0">
         <f>A126*200</f>
@@ -9133,20 +9133,20 @@
     </row>
     <row r="127">
       <c r="A127" s="0" t="n">
-        <v>6.4146309</v>
+        <v>6.438562</v>
       </c>
       <c r="B127" s="0" t="n">
-        <v>0.48336</v>
+        <v>0.47933</v>
       </c>
       <c r="C127" s="0">
         <f>A127*B127</f>
         <v/>
       </c>
       <c r="D127" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E127" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F127" s="0">
         <f>A127*200</f>
@@ -9200,20 +9200,20 @@
     </row>
     <row r="128">
       <c r="A128" s="0" t="n">
-        <v>6.4650396</v>
+        <v>6.4889712</v>
       </c>
       <c r="B128" s="0" t="n">
-        <v>0.48137</v>
+        <v>0.47689</v>
       </c>
       <c r="C128" s="0">
         <f>A128*B128</f>
         <v/>
       </c>
       <c r="D128" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E128" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F128" s="0">
         <f>A128*200</f>
@@ -9267,20 +9267,20 @@
     </row>
     <row r="129">
       <c r="A129" s="0" t="n">
-        <v>6.5190127</v>
+        <v>6.5424355</v>
       </c>
       <c r="B129" s="0" t="n">
-        <v>0.47918</v>
+        <v>0.47484</v>
       </c>
       <c r="C129" s="0">
         <f>A129*B129</f>
         <v/>
       </c>
       <c r="D129" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E129" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F129" s="0">
         <f>A129*200</f>
@@ -9334,20 +9334,20 @@
     </row>
     <row r="130">
       <c r="A130" s="0" t="n">
-        <v>6.5694224</v>
+        <v>6.5948818</v>
       </c>
       <c r="B130" s="0" t="n">
-        <v>0.47691</v>
+        <v>0.47238</v>
       </c>
       <c r="C130" s="0">
         <f>A130*B130</f>
         <v/>
       </c>
       <c r="D130" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E130" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F130" s="0">
         <f>A130*200</f>
@@ -9401,20 +9401,20 @@
     </row>
     <row r="131">
       <c r="A131" s="0" t="n">
-        <v>6.6208496</v>
+        <v>6.6478364</v>
       </c>
       <c r="B131" s="0" t="n">
-        <v>0.47481</v>
+        <v>0.47001</v>
       </c>
       <c r="C131" s="0">
         <f>A131*B131</f>
         <v/>
       </c>
       <c r="D131" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E131" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F131" s="0">
         <f>A131*200</f>
@@ -9468,20 +9468,20 @@
     </row>
     <row r="132">
       <c r="A132" s="0" t="n">
-        <v>6.6717676</v>
+        <v>6.6997734</v>
       </c>
       <c r="B132" s="0" t="n">
-        <v>0.47253</v>
+        <v>0.46778</v>
       </c>
       <c r="C132" s="0">
         <f>A132*B132</f>
         <v/>
       </c>
       <c r="D132" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E132" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F132" s="0">
         <f>A132*200</f>
@@ -9535,20 +9535,20 @@
     </row>
     <row r="133">
       <c r="A133" s="0" t="n">
-        <v>6.7221768</v>
+        <v>6.752728</v>
       </c>
       <c r="B133" s="0" t="n">
-        <v>0.47076</v>
+        <v>0.46524</v>
       </c>
       <c r="C133" s="0">
         <f>A133*B133</f>
         <v/>
       </c>
       <c r="D133" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E133" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F133" s="0">
         <f>A133*200</f>
@@ -9602,20 +9602,20 @@
     </row>
     <row r="134">
       <c r="A134" s="0" t="n">
-        <v>6.774623</v>
+        <v>6.8107749</v>
       </c>
       <c r="B134" s="0" t="n">
-        <v>0.46829</v>
+        <v>0.46295</v>
       </c>
       <c r="C134" s="0">
         <f>A134*B134</f>
         <v/>
       </c>
       <c r="D134" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E134" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F134" s="0">
         <f>A134*200</f>
@@ -9669,20 +9669,20 @@
     </row>
     <row r="135">
       <c r="A135" s="0" t="n">
-        <v>6.8250317</v>
+        <v>6.8616934</v>
       </c>
       <c r="B135" s="0" t="n">
-        <v>0.46652</v>
+        <v>0.46068</v>
       </c>
       <c r="C135" s="0">
         <f>A135*B135</f>
         <v/>
       </c>
       <c r="D135" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E135" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F135" s="0">
         <f>A135*200</f>
@@ -9736,20 +9736,20 @@
     </row>
     <row r="136">
       <c r="A136" s="0" t="n">
-        <v>6.8759512</v>
+        <v>6.9126118</v>
       </c>
       <c r="B136" s="0" t="n">
-        <v>0.46408</v>
+        <v>0.45833</v>
       </c>
       <c r="C136" s="0">
         <f>A136*B136</f>
         <v/>
       </c>
       <c r="D136" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E136" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F136" s="0">
         <f>A136*200</f>
@@ -9803,20 +9803,20 @@
     </row>
     <row r="137">
       <c r="A137" s="0" t="n">
-        <v>6.9299233</v>
+        <v>6.9635298</v>
       </c>
       <c r="B137" s="0" t="n">
-        <v>0.46188</v>
+        <v>0.45617</v>
       </c>
       <c r="C137" s="0">
         <f>A137*B137</f>
         <v/>
       </c>
       <c r="D137" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E137" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F137" s="0">
         <f>A137*200</f>
@@ -9870,20 +9870,20 @@
     </row>
     <row r="138">
       <c r="A138" s="0" t="n">
-        <v>6.9833877</v>
+        <v>7.0154663</v>
       </c>
       <c r="B138" s="0" t="n">
-        <v>0.45961</v>
+        <v>0.45409</v>
       </c>
       <c r="C138" s="0">
         <f>A138*B138</f>
         <v/>
       </c>
       <c r="D138" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E138" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F138" s="0">
         <f>A138*200</f>
@@ -9937,20 +9937,20 @@
     </row>
     <row r="139">
       <c r="A139" s="0" t="n">
-        <v>7.0353247</v>
+        <v>7.0674028</v>
       </c>
       <c r="B139" s="0" t="n">
-        <v>0.45749</v>
+        <v>0.45134</v>
       </c>
       <c r="C139" s="0">
         <f>A139*B139</f>
         <v/>
       </c>
       <c r="D139" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E139" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F139" s="0">
         <f>A139*200</f>
@@ -10004,20 +10004,20 @@
     </row>
     <row r="140">
       <c r="A140" s="0" t="n">
-        <v>7.0857339</v>
+        <v>7.1223945</v>
       </c>
       <c r="B140" s="0" t="n">
-        <v>0.45518</v>
+        <v>0.44945</v>
       </c>
       <c r="C140" s="0">
         <f>A140*B140</f>
         <v/>
       </c>
       <c r="D140" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E140" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F140" s="0">
         <f>A140*200</f>
@@ -10064,20 +10064,20 @@
     </row>
     <row r="141">
       <c r="A141" s="0" t="n">
-        <v>7.1381797</v>
+        <v>7.1738228</v>
       </c>
       <c r="B141" s="0" t="n">
-        <v>0.45333</v>
+        <v>0.44689</v>
       </c>
       <c r="C141" s="0">
         <f>A141*B141</f>
         <v/>
       </c>
       <c r="D141" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E141" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F141" s="0">
         <f>A141*200</f>
@@ -10124,20 +10124,20 @@
     </row>
     <row r="142">
       <c r="A142" s="0" t="n">
-        <v>7.1926621</v>
+        <v>7.2252505</v>
       </c>
       <c r="B142" s="0" t="n">
-        <v>0.45084</v>
+        <v>0.44481</v>
       </c>
       <c r="C142" s="0">
         <f>A142*B142</f>
         <v/>
       </c>
       <c r="D142" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E142" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F142" s="0">
         <f>A142*200</f>
@@ -10184,20 +10184,20 @@
     </row>
     <row r="143">
       <c r="A143" s="0" t="n">
-        <v>7.246126</v>
+        <v>7.2817695</v>
       </c>
       <c r="B143" s="0" t="n">
-        <v>0.44865</v>
+        <v>0.44219</v>
       </c>
       <c r="C143" s="0">
         <f>A143*B143</f>
         <v/>
       </c>
       <c r="D143" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E143" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F143" s="0">
         <f>A143*200</f>
@@ -10244,20 +10244,20 @@
     </row>
     <row r="144">
       <c r="A144" s="0" t="n">
-        <v>7.2980635</v>
+        <v>7.3342158</v>
       </c>
       <c r="B144" s="0" t="n">
-        <v>0.44618</v>
+        <v>0.43985</v>
       </c>
       <c r="C144" s="0">
         <f>A144*B144</f>
         <v/>
       </c>
       <c r="D144" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E144" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F144" s="0">
         <f>A144*200</f>
@@ -10304,20 +10304,20 @@
     </row>
     <row r="145">
       <c r="A145" s="0" t="n">
-        <v>7.3505093</v>
+        <v>7.3846245</v>
       </c>
       <c r="B145" s="0" t="n">
-        <v>0.44428</v>
+        <v>0.43752</v>
       </c>
       <c r="C145" s="0">
         <f>A145*B145</f>
         <v/>
       </c>
       <c r="D145" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E145" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F145" s="0">
         <f>A145*200</f>
@@ -10364,20 +10364,20 @@
     </row>
     <row r="146">
       <c r="A146" s="0" t="n">
-        <v>7.4034639</v>
+        <v>7.4360522</v>
       </c>
       <c r="B146" s="0" t="n">
-        <v>0.44219</v>
+        <v>0.43553</v>
       </c>
       <c r="C146" s="0">
         <f>A146*B146</f>
         <v/>
       </c>
       <c r="D146" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E146" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F146" s="0">
         <f>A146*200</f>
@@ -10424,20 +10424,20 @@
     </row>
     <row r="147">
       <c r="A147" s="0" t="n">
-        <v>7.4543823</v>
+        <v>7.487479</v>
       </c>
       <c r="B147" s="0" t="n">
-        <v>0.43981</v>
+        <v>0.43297</v>
       </c>
       <c r="C147" s="0">
         <f>A147*B147</f>
         <v/>
       </c>
       <c r="D147" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E147" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F147" s="0">
         <f>A147*200</f>
@@ -10484,20 +10484,20 @@
     </row>
     <row r="148">
       <c r="A148" s="0" t="n">
-        <v>7.5078472</v>
+        <v>7.5389072</v>
       </c>
       <c r="B148" s="0" t="n">
-        <v>0.4378</v>
+        <v>0.43064</v>
       </c>
       <c r="C148" s="0">
         <f>A148*B148</f>
         <v/>
       </c>
       <c r="D148" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E148" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F148" s="0">
         <f>A148*200</f>
@@ -10544,20 +10544,20 @@
     </row>
     <row r="149">
       <c r="A149" s="0" t="n">
-        <v>7.5582559</v>
+        <v>7.5913525</v>
       </c>
       <c r="B149" s="0" t="n">
-        <v>0.43547</v>
+        <v>0.42822</v>
       </c>
       <c r="C149" s="0">
         <f>A149*B149</f>
         <v/>
       </c>
       <c r="D149" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E149" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F149" s="0">
         <f>A149*200</f>
@@ -10604,20 +10604,20 @@
     </row>
     <row r="150">
       <c r="A150" s="0" t="n">
-        <v>7.6101924</v>
+        <v>7.6453267</v>
       </c>
       <c r="B150" s="0" t="n">
-        <v>0.43316</v>
+        <v>0.42579</v>
       </c>
       <c r="C150" s="0">
         <f>A150*B150</f>
         <v/>
       </c>
       <c r="D150" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E150" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F150" s="0">
         <f>A150*200</f>
@@ -10664,20 +10664,20 @@
     </row>
     <row r="151">
       <c r="A151" s="0" t="n">
-        <v>7.6631475</v>
+        <v>7.6977725</v>
       </c>
       <c r="B151" s="0" t="n">
-        <v>0.43097</v>
+        <v>0.42371</v>
       </c>
       <c r="C151" s="0">
         <f>A151*B151</f>
         <v/>
       </c>
       <c r="D151" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E151" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F151" s="0">
         <f>A151*200</f>
@@ -10724,20 +10724,20 @@
     </row>
     <row r="152">
       <c r="A152" s="0" t="n">
-        <v>7.715084</v>
+        <v>7.7492002</v>
       </c>
       <c r="B152" s="0" t="n">
-        <v>0.42873</v>
+        <v>0.42142</v>
       </c>
       <c r="C152" s="0">
         <f>A152*B152</f>
         <v/>
       </c>
       <c r="D152" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E152" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F152" s="0">
         <f>A152*200</f>
@@ -10784,20 +10784,20 @@
     </row>
     <row r="153">
       <c r="A153" s="0" t="n">
-        <v>7.7675303</v>
+        <v>7.800627</v>
       </c>
       <c r="B153" s="0" t="n">
-        <v>0.42669</v>
+        <v>0.41928</v>
       </c>
       <c r="C153" s="0">
         <f>A153*B153</f>
         <v/>
       </c>
       <c r="D153" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E153" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F153" s="0">
         <f>A153*200</f>
@@ -10844,20 +10844,20 @@
     </row>
     <row r="154">
       <c r="A154" s="0" t="n">
-        <v>7.8179399</v>
+        <v>7.8525635</v>
       </c>
       <c r="B154" s="0" t="n">
-        <v>0.42432</v>
+        <v>0.41644</v>
       </c>
       <c r="C154" s="0">
         <f>A154*B154</f>
         <v/>
       </c>
       <c r="D154" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E154" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F154" s="0">
         <f>A154*200</f>
@@ -10904,20 +10904,20 @@
     </row>
     <row r="155">
       <c r="A155" s="0" t="n">
-        <v>7.8683486</v>
+        <v>7.9039917</v>
       </c>
       <c r="B155" s="0" t="n">
-        <v>0.42211</v>
+        <v>0.41434</v>
       </c>
       <c r="C155" s="0">
         <f>A155*B155</f>
         <v/>
       </c>
       <c r="D155" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E155" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F155" s="0">
         <f>A155*200</f>
@@ -10964,20 +10964,20 @@
     </row>
     <row r="156">
       <c r="A156" s="0" t="n">
-        <v>7.9207949</v>
+        <v>7.956437</v>
       </c>
       <c r="B156" s="0" t="n">
-        <v>0.42001</v>
+        <v>0.41209</v>
       </c>
       <c r="C156" s="0">
         <f>A156*B156</f>
         <v/>
       </c>
       <c r="D156" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E156" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F156" s="0">
         <f>A156*200</f>
@@ -11024,20 +11024,20 @@
     </row>
     <row r="157">
       <c r="A157" s="0" t="n">
-        <v>7.9722222</v>
+        <v>8.007355499999999</v>
       </c>
       <c r="B157" s="0" t="n">
-        <v>0.418</v>
+        <v>0.40966</v>
       </c>
       <c r="C157" s="0">
         <f>A157*B157</f>
         <v/>
       </c>
       <c r="D157" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E157" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F157" s="0">
         <f>A157*200</f>
@@ -11084,20 +11084,20 @@
     </row>
     <row r="158">
       <c r="A158" s="0" t="n">
-        <v>8.0282319</v>
+        <v>8.059801800000001</v>
       </c>
       <c r="B158" s="0" t="n">
-        <v>0.41546</v>
+        <v>0.40746</v>
       </c>
       <c r="C158" s="0">
         <f>A158*B158</f>
         <v/>
       </c>
       <c r="D158" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E158" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F158" s="0">
         <f>A158*200</f>
@@ -11144,20 +11144,20 @@
     </row>
     <row r="159">
       <c r="A159" s="0" t="n">
-        <v>8.0786411</v>
+        <v>8.111229</v>
       </c>
       <c r="B159" s="0" t="n">
-        <v>0.41314</v>
+        <v>0.40519</v>
       </c>
       <c r="C159" s="0">
         <f>A159*B159</f>
         <v/>
       </c>
       <c r="D159" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E159" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F159" s="0">
         <f>A159*200</f>
@@ -11204,20 +11204,20 @@
     </row>
     <row r="160">
       <c r="A160" s="0" t="n">
-        <v>8.131596699999999</v>
+        <v>8.1631655</v>
       </c>
       <c r="B160" s="0" t="n">
-        <v>0.4109</v>
+        <v>0.40286</v>
       </c>
       <c r="C160" s="0">
         <f>A160*B160</f>
         <v/>
       </c>
       <c r="D160" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E160" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F160" s="0">
         <f>A160*200</f>
@@ -11264,20 +11264,20 @@
     </row>
     <row r="161">
       <c r="A161" s="0" t="n">
-        <v>8.183024400000001</v>
+        <v>8.213575199999999</v>
       </c>
       <c r="B161" s="0" t="n">
-        <v>0.40914</v>
+        <v>0.40055</v>
       </c>
       <c r="C161" s="0">
         <f>A161*B161</f>
         <v/>
       </c>
       <c r="D161" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E161" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F161" s="0">
         <f>A161*200</f>
@@ -11324,20 +11324,20 @@
     </row>
     <row r="162">
       <c r="A162" s="0" t="n">
-        <v>8.234451200000001</v>
+        <v>8.2639844</v>
       </c>
       <c r="B162" s="0" t="n">
-        <v>0.40638</v>
+        <v>0.39803</v>
       </c>
       <c r="C162" s="0">
         <f>A162*B162</f>
         <v/>
       </c>
       <c r="D162" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E162" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F162" s="0">
         <f>A162*200</f>
@@ -11384,20 +11384,20 @@
     </row>
     <row r="163">
       <c r="A163" s="0" t="n">
-        <v>8.2853701</v>
+        <v>8.3149023</v>
       </c>
       <c r="B163" s="0" t="n">
-        <v>0.40435</v>
+        <v>0.39586</v>
       </c>
       <c r="C163" s="0">
         <f>A163*B163</f>
         <v/>
       </c>
       <c r="D163" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E163" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F163" s="0">
         <f>A163*200</f>
@@ -11444,20 +11444,20 @@
     </row>
     <row r="164">
       <c r="A164" s="0" t="n">
-        <v>8.3357793</v>
+        <v>8.3673486</v>
       </c>
       <c r="B164" s="0" t="n">
-        <v>0.40214</v>
+        <v>0.39364</v>
       </c>
       <c r="C164" s="0">
         <f>A164*B164</f>
         <v/>
       </c>
       <c r="D164" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E164" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F164" s="0">
         <f>A164*200</f>
@@ -11504,20 +11504,20 @@
     </row>
     <row r="165">
       <c r="A165" s="0" t="n">
-        <v>8.387207</v>
+        <v>8.4177578</v>
       </c>
       <c r="B165" s="0" t="n">
-        <v>0.39996</v>
+        <v>0.39114</v>
       </c>
       <c r="C165" s="0">
         <f>A165*B165</f>
         <v/>
       </c>
       <c r="D165" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E165" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F165" s="0">
         <f>A165*200</f>
@@ -11564,20 +11564,20 @@
     </row>
     <row r="166">
       <c r="A166" s="0" t="n">
-        <v>8.4432168</v>
+        <v>8.4712227</v>
       </c>
       <c r="B166" s="0" t="n">
-        <v>0.39757</v>
+        <v>0.38894</v>
       </c>
       <c r="C166" s="0">
         <f>A166*B166</f>
         <v/>
       </c>
       <c r="D166" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E166" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F166" s="0">
         <f>A166*200</f>
@@ -11624,20 +11624,20 @@
     </row>
     <row r="167">
       <c r="A167" s="0" t="n">
-        <v>8.494135699999999</v>
+        <v>8.5221406</v>
       </c>
       <c r="B167" s="0" t="n">
-        <v>0.39528</v>
+        <v>0.38652</v>
       </c>
       <c r="C167" s="0">
         <f>A167*B167</f>
         <v/>
       </c>
       <c r="D167" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E167" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F167" s="0">
         <f>A167*200</f>
@@ -11684,20 +11684,20 @@
     </row>
     <row r="168">
       <c r="A168" s="0" t="n">
-        <v>8.5450537</v>
+        <v>8.5761143</v>
       </c>
       <c r="B168" s="0" t="n">
-        <v>0.39326</v>
+        <v>0.38429</v>
       </c>
       <c r="C168" s="0">
         <f>A168*B168</f>
         <v/>
       </c>
       <c r="D168" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E168" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F168" s="0">
         <f>A168*200</f>
@@ -11744,20 +11744,20 @@
     </row>
     <row r="169">
       <c r="A169" s="0" t="n">
-        <v>8.595462899999999</v>
+        <v>8.6270322</v>
       </c>
       <c r="B169" s="0" t="n">
-        <v>0.39101</v>
+        <v>0.38169</v>
       </c>
       <c r="C169" s="0">
         <f>A169*B169</f>
         <v/>
       </c>
       <c r="D169" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E169" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F169" s="0">
         <f>A169*200</f>
@@ -11804,20 +11804,20 @@
     </row>
     <row r="170">
       <c r="A170" s="0" t="n">
-        <v>8.648417999999999</v>
+        <v>8.6794785</v>
       </c>
       <c r="B170" s="0" t="n">
-        <v>0.38862</v>
+        <v>0.37955</v>
       </c>
       <c r="C170" s="0">
         <f>A170*B170</f>
         <v/>
       </c>
       <c r="D170" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E170" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F170" s="0">
         <f>A170*200</f>
@@ -11864,20 +11864,20 @@
     </row>
     <row r="171">
       <c r="A171" s="0" t="n">
-        <v>8.698827100000001</v>
+        <v>8.731923800000001</v>
       </c>
       <c r="B171" s="0" t="n">
-        <v>0.38663</v>
+        <v>0.37701</v>
       </c>
       <c r="C171" s="0">
         <f>A171*B171</f>
         <v/>
       </c>
       <c r="D171" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E171" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F171" s="0">
         <f>A171*200</f>
@@ -11924,20 +11924,20 @@
     </row>
     <row r="172">
       <c r="A172" s="0" t="n">
-        <v>8.7492363</v>
+        <v>8.786916</v>
       </c>
       <c r="B172" s="0" t="n">
-        <v>0.38421</v>
+        <v>0.37451</v>
       </c>
       <c r="C172" s="0">
         <f>A172*B172</f>
         <v/>
       </c>
       <c r="D172" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E172" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F172" s="0">
         <f>A172*200</f>
@@ -11984,20 +11984,20 @@
     </row>
     <row r="173">
       <c r="A173" s="0" t="n">
-        <v>8.8016816</v>
+        <v>8.837835</v>
       </c>
       <c r="B173" s="0" t="n">
-        <v>0.38219</v>
+        <v>0.37228</v>
       </c>
       <c r="C173" s="0">
         <f>A173*B173</f>
         <v/>
       </c>
       <c r="D173" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E173" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F173" s="0">
         <f>A173*200</f>
@@ -12044,20 +12044,20 @@
     </row>
     <row r="174">
       <c r="A174" s="0" t="n">
-        <v>8.8531104</v>
+        <v>8.890280300000001</v>
       </c>
       <c r="B174" s="0" t="n">
-        <v>0.3797</v>
+        <v>0.36995</v>
       </c>
       <c r="C174" s="0">
         <f>A174*B174</f>
         <v/>
       </c>
       <c r="D174" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E174" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F174" s="0">
         <f>A174*200</f>
@@ -12104,20 +12104,20 @@
     </row>
     <row r="175">
       <c r="A175" s="0" t="n">
-        <v>8.904027299999999</v>
+        <v>8.9406885</v>
       </c>
       <c r="B175" s="0" t="n">
-        <v>0.37751</v>
+        <v>0.36747</v>
       </c>
       <c r="C175" s="0">
         <f>A175*B175</f>
         <v/>
       </c>
       <c r="D175" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E175" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F175" s="0">
         <f>A175*200</f>
@@ -12164,20 +12164,20 @@
     </row>
     <row r="176">
       <c r="A176" s="0" t="n">
-        <v>8.9544365</v>
+        <v>8.9946631</v>
       </c>
       <c r="B176" s="0" t="n">
-        <v>0.37525</v>
+        <v>0.36519</v>
       </c>
       <c r="C176" s="0">
         <f>A176*B176</f>
         <v/>
       </c>
       <c r="D176" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E176" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F176" s="0">
         <f>A176*200</f>
@@ -12224,20 +12224,20 @@
     </row>
     <row r="177">
       <c r="A177" s="0" t="n">
-        <v>9.005865200000001</v>
+        <v>9.0506729</v>
       </c>
       <c r="B177" s="0" t="n">
-        <v>0.37317</v>
+        <v>0.36246</v>
       </c>
       <c r="C177" s="0">
         <f>A177*B177</f>
         <v/>
       </c>
       <c r="D177" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E177" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F177" s="0">
         <f>A177*200</f>
@@ -12284,20 +12284,20 @@
     </row>
     <row r="178">
       <c r="A178" s="0" t="n">
-        <v>9.056782200000001</v>
+        <v>9.101082</v>
       </c>
       <c r="B178" s="0" t="n">
-        <v>0.37077</v>
+        <v>0.36</v>
       </c>
       <c r="C178" s="0">
         <f>A178*B178</f>
         <v/>
       </c>
       <c r="D178" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E178" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F178" s="0">
         <f>A178*200</f>
@@ -12344,20 +12344,20 @@
     </row>
     <row r="179">
       <c r="A179" s="0" t="n">
-        <v>9.1122842</v>
+        <v>9.153018599999999</v>
       </c>
       <c r="B179" s="0" t="n">
-        <v>0.36853</v>
+        <v>0.3578</v>
       </c>
       <c r="C179" s="0">
         <f>A179*B179</f>
         <v/>
       </c>
       <c r="D179" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E179" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F179" s="0">
         <f>A179*200</f>
@@ -12404,20 +12404,20 @@
     </row>
     <row r="180">
       <c r="A180" s="0" t="n">
-        <v>9.1682939</v>
+        <v>9.207501000000001</v>
       </c>
       <c r="B180" s="0" t="n">
-        <v>0.36603</v>
+        <v>0.35542</v>
       </c>
       <c r="C180" s="0">
         <f>A180*B180</f>
         <v/>
       </c>
       <c r="D180" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E180" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F180" s="0">
         <f>A180*200</f>
@@ -12464,20 +12464,20 @@
     </row>
     <row r="181">
       <c r="A181" s="0" t="n">
-        <v>9.222776400000001</v>
+        <v>9.2624932</v>
       </c>
       <c r="B181" s="0" t="n">
-        <v>0.3633</v>
+        <v>0.35273</v>
       </c>
       <c r="C181" s="0">
         <f>A181*B181</f>
         <v/>
       </c>
       <c r="D181" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E181" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F181" s="0">
         <f>A181*200</f>
@@ -12524,20 +12524,20 @@
     </row>
     <row r="182">
       <c r="A182" s="0" t="n">
-        <v>9.276241199999999</v>
+        <v>9.3185029</v>
       </c>
       <c r="B182" s="0" t="n">
-        <v>0.3612</v>
+        <v>0.35042</v>
       </c>
       <c r="C182" s="0">
         <f>A182*B182</f>
         <v/>
       </c>
       <c r="D182" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E182" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F182" s="0">
         <f>A182*200</f>
@@ -12584,20 +12584,20 @@
     </row>
     <row r="183">
       <c r="A183" s="0" t="n">
-        <v>9.327667999999999</v>
+        <v>9.3704404</v>
       </c>
       <c r="B183" s="0" t="n">
-        <v>0.35872</v>
+        <v>0.34789</v>
       </c>
       <c r="C183" s="0">
         <f>A183*B183</f>
         <v/>
       </c>
       <c r="D183" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E183" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F183" s="0">
         <f>A183*200</f>
@@ -12644,20 +12644,20 @@
     </row>
     <row r="184">
       <c r="A184" s="0" t="n">
-        <v>9.3780781</v>
+        <v>9.421358400000001</v>
       </c>
       <c r="B184" s="0" t="n">
-        <v>0.35652</v>
+        <v>0.34534</v>
       </c>
       <c r="C184" s="0">
         <f>A184*B184</f>
         <v/>
       </c>
       <c r="D184" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E184" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F184" s="0">
         <f>A184*200</f>
@@ -12704,20 +12704,20 @@
     </row>
     <row r="185">
       <c r="A185" s="0" t="n">
-        <v>9.4295049</v>
+        <v>9.4727861</v>
       </c>
       <c r="B185" s="0" t="n">
-        <v>0.35427</v>
+        <v>0.34331</v>
       </c>
       <c r="C185" s="0">
         <f>A185*B185</f>
         <v/>
       </c>
       <c r="D185" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E185" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F185" s="0">
         <f>A185*200</f>
@@ -12764,20 +12764,20 @@
     </row>
     <row r="186">
       <c r="A186" s="0" t="n">
-        <v>9.480932599999999</v>
+        <v>9.5237041</v>
       </c>
       <c r="B186" s="0" t="n">
-        <v>0.35194</v>
+        <v>0.34064</v>
       </c>
       <c r="C186" s="0">
         <f>A186*B186</f>
         <v/>
       </c>
       <c r="D186" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E186" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F186" s="0">
         <f>A186*200</f>
@@ -12824,20 +12824,20 @@
     </row>
     <row r="187">
       <c r="A187" s="0" t="n">
-        <v>9.5333779</v>
+        <v>9.577676800000001</v>
       </c>
       <c r="B187" s="0" t="n">
-        <v>0.34994</v>
+        <v>0.33816</v>
       </c>
       <c r="C187" s="0">
         <f>A187*B187</f>
         <v/>
       </c>
       <c r="D187" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E187" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F187" s="0">
         <f>A187*200</f>
@@ -12884,20 +12884,20 @@
     </row>
     <row r="188">
       <c r="A188" s="0" t="n">
-        <v>9.585314500000001</v>
+        <v>9.6296143</v>
       </c>
       <c r="B188" s="0" t="n">
-        <v>0.34738</v>
+        <v>0.33585</v>
       </c>
       <c r="C188" s="0">
         <f>A188*B188</f>
         <v/>
       </c>
       <c r="D188" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E188" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F188" s="0">
         <f>A188*200</f>
@@ -12944,20 +12944,20 @@
     </row>
     <row r="189">
       <c r="A189" s="0" t="n">
-        <v>9.638270500000001</v>
+        <v>9.686132799999999</v>
       </c>
       <c r="B189" s="0" t="n">
-        <v>0.34486</v>
+        <v>0.33325</v>
       </c>
       <c r="C189" s="0">
         <f>A189*B189</f>
         <v/>
       </c>
       <c r="D189" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E189" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F189" s="0">
         <f>A189*200</f>
@@ -13004,20 +13004,20 @@
     </row>
     <row r="190">
       <c r="A190" s="0" t="n">
-        <v>9.6896982</v>
+        <v>9.736542999999999</v>
       </c>
       <c r="B190" s="0" t="n">
-        <v>0.34272</v>
+        <v>0.33065</v>
       </c>
       <c r="C190" s="0">
         <f>A190*B190</f>
         <v/>
       </c>
       <c r="D190" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E190" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F190" s="0">
         <f>A190*200</f>
@@ -13064,20 +13064,20 @@
     </row>
     <row r="191">
       <c r="A191" s="0" t="n">
-        <v>9.743162099999999</v>
+        <v>9.7900068</v>
       </c>
       <c r="B191" s="0" t="n">
-        <v>0.34043</v>
+        <v>0.32859</v>
       </c>
       <c r="C191" s="0">
         <f>A191*B191</f>
         <v/>
       </c>
       <c r="D191" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E191" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F191" s="0">
         <f>A191*200</f>
@@ -13124,20 +13124,20 @@
     </row>
     <row r="192">
       <c r="A192" s="0" t="n">
-        <v>9.7935713</v>
+        <v>9.8429629</v>
       </c>
       <c r="B192" s="0" t="n">
-        <v>0.33795</v>
+        <v>0.32592</v>
       </c>
       <c r="C192" s="0">
         <f>A192*B192</f>
         <v/>
       </c>
       <c r="D192" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E192" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F192" s="0">
         <f>A192*200</f>
@@ -13184,20 +13184,20 @@
     </row>
     <row r="193">
       <c r="A193" s="0" t="n">
-        <v>9.8465264</v>
+        <v>9.8964268</v>
       </c>
       <c r="B193" s="0" t="n">
-        <v>0.33569</v>
+        <v>0.32328</v>
       </c>
       <c r="C193" s="0">
         <f>A193*B193</f>
         <v/>
       </c>
       <c r="D193" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E193" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F193" s="0">
         <f>A193*200</f>
@@ -13244,20 +13244,20 @@
     </row>
     <row r="194">
       <c r="A194" s="0" t="n">
-        <v>9.8974443</v>
+        <v>9.9468359</v>
       </c>
       <c r="B194" s="0" t="n">
-        <v>0.33346</v>
+        <v>0.32071</v>
       </c>
       <c r="C194" s="0">
         <f>A194*B194</f>
         <v/>
       </c>
       <c r="D194" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E194" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F194" s="0">
         <f>A194*200</f>
@@ -13304,20 +13304,20 @@
     </row>
     <row r="195">
       <c r="A195" s="0" t="n">
-        <v>9.9529453</v>
+        <v>9.9992813</v>
       </c>
       <c r="B195" s="0" t="n">
-        <v>0.33096</v>
+        <v>0.31834</v>
       </c>
       <c r="C195" s="0">
         <f>A195*B195</f>
         <v/>
       </c>
       <c r="D195" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E195" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F195" s="0">
         <f>A195*200</f>
@@ -13364,20 +13364,20 @@
     </row>
     <row r="196">
       <c r="A196" s="0" t="n">
-        <v>10.003863</v>
+        <v>10.050199</v>
       </c>
       <c r="B196" s="0" t="n">
-        <v>0.32838</v>
+        <v>0.3163</v>
       </c>
       <c r="C196" s="0">
         <f>A196*B196</f>
         <v/>
       </c>
       <c r="D196" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E196" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F196" s="0">
         <f>A196*200</f>
@@ -13424,20 +13424,20 @@
     </row>
     <row r="197">
       <c r="A197" s="0" t="n">
-        <v>10.054272</v>
+        <v>10.100608</v>
       </c>
       <c r="B197" s="0" t="n">
-        <v>0.32638</v>
+        <v>0.31383</v>
       </c>
       <c r="C197" s="0">
         <f>A197*B197</f>
         <v/>
       </c>
       <c r="D197" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E197" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F197" s="0">
         <f>A197*200</f>
@@ -13484,20 +13484,20 @@
     </row>
     <row r="198">
       <c r="A198" s="0" t="n">
-        <v>10.10519</v>
+        <v>10.152546</v>
       </c>
       <c r="B198" s="0" t="n">
-        <v>0.32407</v>
+        <v>0.31152</v>
       </c>
       <c r="C198" s="0">
         <f>A198*B198</f>
         <v/>
       </c>
       <c r="D198" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E198" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F198" s="0">
         <f>A198*200</f>
@@ -13544,20 +13544,20 @@
     </row>
     <row r="199">
       <c r="A199" s="0" t="n">
-        <v>10.156619</v>
+        <v>10.203463</v>
       </c>
       <c r="B199" s="0" t="n">
-        <v>0.3217</v>
+        <v>0.30887</v>
       </c>
       <c r="C199" s="0">
         <f>A199*B199</f>
         <v/>
       </c>
       <c r="D199" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E199" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F199" s="0">
         <f>A199*200</f>
@@ -13604,20 +13604,20 @@
     </row>
     <row r="200">
       <c r="A200" s="0" t="n">
-        <v>10.208047</v>
+        <v>10.257437</v>
       </c>
       <c r="B200" s="0" t="n">
-        <v>0.31924</v>
+        <v>0.30654</v>
       </c>
       <c r="C200" s="0">
         <f>A200*B200</f>
         <v/>
       </c>
       <c r="D200" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E200" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F200" s="0">
         <f>A200*200</f>
@@ -13664,20 +13664,20 @@
     </row>
     <row r="201">
       <c r="A201" s="0" t="n">
-        <v>10.260492</v>
+        <v>10.3109</v>
       </c>
       <c r="B201" s="0" t="n">
-        <v>0.31683</v>
+        <v>0.30394</v>
       </c>
       <c r="C201" s="0">
         <f>A201*B201</f>
         <v/>
       </c>
       <c r="D201" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E201" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F201" s="0">
         <f>A201*200</f>
@@ -13724,20 +13724,20 @@
     </row>
     <row r="202">
       <c r="A202" s="0" t="n">
-        <v>10.311411</v>
+        <v>10.365894</v>
       </c>
       <c r="B202" s="0" t="n">
-        <v>0.3145</v>
+        <v>0.30125</v>
       </c>
       <c r="C202" s="0">
         <f>A202*B202</f>
         <v/>
       </c>
       <c r="D202" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E202" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F202" s="0">
         <f>A202*200</f>
@@ -13784,20 +13784,20 @@
     </row>
     <row r="203">
       <c r="A203" s="0" t="n">
-        <v>10.361819</v>
+        <v>10.418339</v>
       </c>
       <c r="B203" s="0" t="n">
-        <v>0.31229</v>
+        <v>0.29892</v>
       </c>
       <c r="C203" s="0">
         <f>A203*B203</f>
         <v/>
       </c>
       <c r="D203" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E203" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F203" s="0">
         <f>A203*200</f>
@@ -13844,20 +13844,20 @@
     </row>
     <row r="204">
       <c r="A204" s="0" t="n">
-        <v>10.412229</v>
+        <v>10.469257</v>
       </c>
       <c r="B204" s="0" t="n">
-        <v>0.3098</v>
+        <v>0.29631</v>
       </c>
       <c r="C204" s="0">
         <f>A204*B204</f>
         <v/>
       </c>
       <c r="D204" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E204" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F204" s="0">
         <f>A204*200</f>
@@ -13904,20 +13904,20 @@
     </row>
     <row r="205">
       <c r="A205" s="0" t="n">
-        <v>10.462638</v>
+        <v>10.520175</v>
       </c>
       <c r="B205" s="0" t="n">
-        <v>0.30769</v>
+        <v>0.29396</v>
       </c>
       <c r="C205" s="0">
         <f>A205*B205</f>
         <v/>
       </c>
       <c r="D205" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E205" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F205" s="0">
         <f>A205*200</f>
@@ -13964,20 +13964,20 @@
     </row>
     <row r="206">
       <c r="A206" s="0" t="n">
-        <v>10.514065</v>
+        <v>10.570585</v>
       </c>
       <c r="B206" s="0" t="n">
-        <v>0.30541</v>
+        <v>0.29174</v>
       </c>
       <c r="C206" s="0">
         <f>A206*B206</f>
         <v/>
       </c>
       <c r="D206" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E206" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F206" s="0">
         <f>A206*200</f>
@@ -14024,20 +14024,20 @@
     </row>
     <row r="207">
       <c r="A207" s="0" t="n">
-        <v>10.564983</v>
+        <v>10.622521</v>
       </c>
       <c r="B207" s="0" t="n">
-        <v>0.30297</v>
+        <v>0.28917</v>
       </c>
       <c r="C207" s="0">
         <f>A207*B207</f>
         <v/>
       </c>
       <c r="D207" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E207" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F207" s="0">
         <f>A207*200</f>
@@ -14084,20 +14084,20 @@
     </row>
     <row r="208">
       <c r="A208" s="0" t="n">
-        <v>10.616411</v>
+        <v>10.674967</v>
       </c>
       <c r="B208" s="0" t="n">
-        <v>0.30053</v>
+        <v>0.28672</v>
       </c>
       <c r="C208" s="0">
         <f>A208*B208</f>
         <v/>
       </c>
       <c r="D208" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E208" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F208" s="0">
         <f>A208*200</f>
@@ -14144,20 +14144,20 @@
     </row>
     <row r="209">
       <c r="A209" s="0" t="n">
-        <v>10.674967</v>
+        <v>10.726394</v>
       </c>
       <c r="B209" s="0" t="n">
-        <v>0.29804</v>
+        <v>0.28414</v>
       </c>
       <c r="C209" s="0">
         <f>A209*B209</f>
         <v/>
       </c>
       <c r="D209" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E209" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F209" s="0">
         <f>A209*200</f>
@@ -14204,20 +14204,20 @@
     </row>
     <row r="210">
       <c r="A210" s="0" t="n">
-        <v>10.726394</v>
+        <v>10.779859</v>
       </c>
       <c r="B210" s="0" t="n">
-        <v>0.29558</v>
+        <v>0.28164</v>
       </c>
       <c r="C210" s="0">
         <f>A210*B210</f>
         <v/>
       </c>
       <c r="D210" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E210" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F210" s="0">
         <f>A210*200</f>
@@ -14264,20 +14264,20 @@
     </row>
     <row r="211">
       <c r="A211" s="0" t="n">
-        <v>10.777313</v>
+        <v>10.831795</v>
       </c>
       <c r="B211" s="0" t="n">
-        <v>0.29329</v>
+        <v>0.27905</v>
       </c>
       <c r="C211" s="0">
         <f>A211*B211</f>
         <v/>
       </c>
       <c r="D211" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E211" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F211" s="0">
         <f>A211*200</f>
@@ -14324,20 +14324,20 @@
     </row>
     <row r="212">
       <c r="A212" s="0" t="n">
-        <v>10.827722</v>
+        <v>10.884241</v>
       </c>
       <c r="B212" s="0" t="n">
-        <v>0.29085</v>
+        <v>0.27653</v>
       </c>
       <c r="C212" s="0">
         <f>A212*B212</f>
         <v/>
       </c>
       <c r="D212" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E212" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F212" s="0">
         <f>A212*200</f>
@@ -14384,20 +14384,20 @@
     </row>
     <row r="213">
       <c r="A213" s="0" t="n">
-        <v>10.878132</v>
+        <v>10.937705</v>
       </c>
       <c r="B213" s="0" t="n">
-        <v>0.2884</v>
+        <v>0.2742</v>
       </c>
       <c r="C213" s="0">
         <f>A213*B213</f>
         <v/>
       </c>
       <c r="D213" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E213" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F213" s="0">
         <f>A213*200</f>
@@ -14444,20 +14444,20 @@
     </row>
     <row r="214">
       <c r="A214" s="0" t="n">
-        <v>10.928541</v>
+        <v>10.988115</v>
       </c>
       <c r="B214" s="0" t="n">
-        <v>0.28582</v>
+        <v>0.2716</v>
       </c>
       <c r="C214" s="0">
         <f>A214*B214</f>
         <v/>
       </c>
       <c r="D214" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E214" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F214" s="0">
         <f>A214*200</f>
@@ -14504,20 +14504,20 @@
     </row>
     <row r="215">
       <c r="A215" s="0" t="n">
-        <v>10.979459</v>
+        <v>11.039542</v>
       </c>
       <c r="B215" s="0" t="n">
-        <v>0.28376</v>
+        <v>0.26912</v>
       </c>
       <c r="C215" s="0">
         <f>A215*B215</f>
         <v/>
       </c>
       <c r="D215" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E215" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F215" s="0">
         <f>A215*200</f>
@@ -14564,20 +14564,20 @@
     </row>
     <row r="216">
       <c r="A216" s="0" t="n">
-        <v>11.033432</v>
+        <v>11.090971</v>
       </c>
       <c r="B216" s="0" t="n">
-        <v>0.28143</v>
+        <v>0.26686</v>
       </c>
       <c r="C216" s="0">
         <f>A216*B216</f>
         <v/>
       </c>
       <c r="D216" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E216" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F216" s="0">
         <f>A216*200</f>
@@ -14624,20 +14624,20 @@
     </row>
     <row r="217">
       <c r="A217" s="0" t="n">
-        <v>11.084351</v>
+        <v>11.141889</v>
       </c>
       <c r="B217" s="0" t="n">
-        <v>0.27874</v>
+        <v>0.26444</v>
       </c>
       <c r="C217" s="0">
         <f>A217*B217</f>
         <v/>
       </c>
       <c r="D217" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E217" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F217" s="0">
         <f>A217*200</f>
@@ -14684,20 +14684,20 @@
     </row>
     <row r="218">
       <c r="A218" s="0" t="n">
-        <v>11.135777</v>
+        <v>11.194335</v>
       </c>
       <c r="B218" s="0" t="n">
-        <v>0.27653</v>
+        <v>0.26196</v>
       </c>
       <c r="C218" s="0">
         <f>A218*B218</f>
         <v/>
       </c>
       <c r="D218" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E218" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F218" s="0">
         <f>A218*200</f>
@@ -14744,20 +14744,20 @@
     </row>
     <row r="219">
       <c r="A219" s="0" t="n">
-        <v>11.186697</v>
+        <v>11.247288</v>
       </c>
       <c r="B219" s="0" t="n">
-        <v>0.27418</v>
+        <v>0.25904</v>
       </c>
       <c r="C219" s="0">
         <f>A219*B219</f>
         <v/>
       </c>
       <c r="D219" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E219" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F219" s="0">
         <f>A219*200</f>
@@ -14804,20 +14804,20 @@
     </row>
     <row r="220">
       <c r="A220" s="0" t="n">
-        <v>11.239143</v>
+        <v>11.297698</v>
       </c>
       <c r="B220" s="0" t="n">
-        <v>0.2715</v>
+        <v>0.25676</v>
       </c>
       <c r="C220" s="0">
         <f>A220*B220</f>
         <v/>
       </c>
       <c r="D220" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E220" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F220" s="0">
         <f>A220*200</f>
@@ -14864,20 +14864,20 @@
     </row>
     <row r="221">
       <c r="A221" s="0" t="n">
-        <v>11.291079</v>
+        <v>11.350145</v>
       </c>
       <c r="B221" s="0" t="n">
-        <v>0.26933</v>
+        <v>0.25426</v>
       </c>
       <c r="C221" s="0">
         <f>A221*B221</f>
         <v/>
       </c>
       <c r="D221" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E221" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F221" s="0">
         <f>A221*200</f>
@@ -14924,20 +14924,20 @@
     </row>
     <row r="222">
       <c r="A222" s="0" t="n">
-        <v>11.341489</v>
+        <v>11.400554</v>
       </c>
       <c r="B222" s="0" t="n">
-        <v>0.26681</v>
+        <v>0.2518</v>
       </c>
       <c r="C222" s="0">
         <f>A222*B222</f>
         <v/>
       </c>
       <c r="D222" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E222" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F222" s="0">
         <f>A222*200</f>
@@ -14984,20 +14984,20 @@
     </row>
     <row r="223">
       <c r="A223" s="0" t="n">
-        <v>11.392916</v>
+        <v>11.395971</v>
       </c>
       <c r="B223" s="0" t="n">
-        <v>0.26459</v>
+        <v>0.25148</v>
       </c>
       <c r="C223" s="0">
         <f>A223*B223</f>
         <v/>
       </c>
       <c r="D223" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E223" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.01476</v>
       </c>
       <c r="F223" s="0">
         <f>A223*200</f>
@@ -15043,21 +15043,15 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="0" t="n">
-        <v>11.44638</v>
-      </c>
-      <c r="B224" s="0" t="n">
-        <v>0.26184</v>
-      </c>
       <c r="C224" s="0">
         <f>A224*B224</f>
         <v/>
       </c>
       <c r="D224" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E224" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.015</v>
       </c>
       <c r="F224" s="0">
         <f>A224*200</f>
@@ -15103,21 +15097,15 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="0" t="n">
-        <v>11.497299</v>
-      </c>
-      <c r="B225" s="0" t="n">
-        <v>0.2594</v>
-      </c>
       <c r="C225" s="0">
         <f>A225*B225</f>
         <v/>
       </c>
       <c r="D225" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E225" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.015</v>
       </c>
       <c r="F225" s="0">
         <f>A225*200</f>
@@ -15167,21 +15155,15 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="0" t="n">
-        <v>11.55229</v>
-      </c>
-      <c r="B226" s="0" t="n">
-        <v>0.2569</v>
-      </c>
       <c r="C226" s="0">
         <f>A226*B226</f>
         <v/>
       </c>
       <c r="D226" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E226" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.015</v>
       </c>
       <c r="F226" s="0">
         <f>A226*200</f>
@@ -15227,21 +15209,15 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="0" t="n">
-        <v>11.605754</v>
-      </c>
-      <c r="B227" s="0" t="n">
-        <v>0.25451</v>
-      </c>
       <c r="C227" s="0">
         <f>A227*B227</f>
         <v/>
       </c>
       <c r="D227" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E227" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.015</v>
       </c>
       <c r="F227" s="0">
         <f>A227*200</f>
@@ -15287,21 +15263,15 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="0" t="n">
-        <v>11.657691</v>
-      </c>
-      <c r="B228" s="0" t="n">
-        <v>0.2518</v>
-      </c>
       <c r="C228" s="0">
         <f>A228*B228</f>
         <v/>
       </c>
       <c r="D228" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E228" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.015</v>
       </c>
       <c r="F228" s="0">
         <f>A228*200</f>
@@ -15347,21 +15317,15 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="0" t="n">
-        <v>11.655654</v>
-      </c>
-      <c r="B229" s="0" t="n">
-        <v>0.25161</v>
-      </c>
       <c r="C229" s="0">
         <f>A229*B229</f>
         <v/>
       </c>
       <c r="D229" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E229" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.015</v>
       </c>
       <c r="F229" s="0">
         <f>A229*200</f>
@@ -15412,10 +15376,10 @@
         <v/>
       </c>
       <c r="D230" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E230" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.015</v>
       </c>
       <c r="F230" s="0">
         <f>A230*200</f>
@@ -15466,10 +15430,10 @@
         <v/>
       </c>
       <c r="D231" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E231" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.015</v>
       </c>
       <c r="F231" s="0">
         <f>A231*200</f>
@@ -15520,10 +15484,10 @@
         <v/>
       </c>
       <c r="D232" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E232" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.015</v>
       </c>
       <c r="F232" s="0">
         <f>A232*200</f>
@@ -15574,10 +15538,10 @@
         <v/>
       </c>
       <c r="D233" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E233" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.015</v>
       </c>
       <c r="F233" s="0">
         <f>A233*200</f>
@@ -15628,10 +15592,10 @@
         <v/>
       </c>
       <c r="D234" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E234" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.015</v>
       </c>
       <c r="F234" s="0">
         <f>A234*200</f>
@@ -15682,10 +15646,10 @@
         <v/>
       </c>
       <c r="D235" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E235" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.015</v>
       </c>
       <c r="F235" s="0">
         <f>A235*200</f>
@@ -15736,10 +15700,10 @@
         <v/>
       </c>
       <c r="D236" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E236" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.015</v>
       </c>
       <c r="F236" s="0">
         <f>A236*200</f>
@@ -15790,10 +15754,10 @@
         <v/>
       </c>
       <c r="D237" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E237" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.015</v>
       </c>
       <c r="F237" s="0">
         <f>A237*200</f>
@@ -15844,10 +15808,10 @@
         <v/>
       </c>
       <c r="D238" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E238" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.015</v>
       </c>
       <c r="F238" s="0">
         <f>A238*200</f>
@@ -15898,10 +15862,10 @@
         <v/>
       </c>
       <c r="D239" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E239" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.015</v>
       </c>
       <c r="F239" s="0">
         <f>A239*200</f>
@@ -15952,10 +15916,10 @@
         <v/>
       </c>
       <c r="D240" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E240" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.015</v>
       </c>
       <c r="F240" s="0">
         <f>A240*200</f>
@@ -16006,10 +15970,10 @@
         <v/>
       </c>
       <c r="D241" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E241" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.015</v>
       </c>
       <c r="F241" s="0">
         <f>A241*200</f>
@@ -16060,10 +16024,10 @@
         <v/>
       </c>
       <c r="D242" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E242" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.015</v>
       </c>
       <c r="F242" s="0">
         <f>A242*200</f>
@@ -16114,10 +16078,10 @@
         <v/>
       </c>
       <c r="D243" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E243" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.015</v>
       </c>
       <c r="F243" s="0">
         <f>A243*200</f>
@@ -16168,10 +16132,10 @@
         <v/>
       </c>
       <c r="D244" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E244" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.015</v>
       </c>
       <c r="F244" s="0">
         <f>A244*200</f>
@@ -16222,10 +16186,10 @@
         <v/>
       </c>
       <c r="D245" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E245" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.015</v>
       </c>
       <c r="F245" s="0">
         <f>A245*200</f>
@@ -16276,10 +16240,10 @@
         <v/>
       </c>
       <c r="D246" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E246" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.015</v>
       </c>
       <c r="F246" s="0">
         <f>A246*200</f>
@@ -16330,10 +16294,10 @@
         <v/>
       </c>
       <c r="D247" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E247" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.015</v>
       </c>
       <c r="F247" s="0">
         <f>A247*200</f>
@@ -16384,10 +16348,10 @@
         <v/>
       </c>
       <c r="D248" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E248" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.015</v>
       </c>
       <c r="F248" s="0">
         <f>A248*200</f>
@@ -16438,10 +16402,10 @@
         <v/>
       </c>
       <c r="D249" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E249" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.015</v>
       </c>
       <c r="F249" s="0">
         <f>A249*200</f>
@@ -16492,10 +16456,10 @@
         <v/>
       </c>
       <c r="D250" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E250" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.015</v>
       </c>
       <c r="F250" s="0">
         <f>A250*200</f>
@@ -16546,10 +16510,10 @@
         <v/>
       </c>
       <c r="D251" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E251" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.015</v>
       </c>
       <c r="F251" s="0">
         <f>A251*200</f>
@@ -16600,10 +16564,10 @@
         <v/>
       </c>
       <c r="D252" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E252" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.015</v>
       </c>
       <c r="F252" s="0">
         <f>A252*200</f>
@@ -16654,10 +16618,10 @@
         <v/>
       </c>
       <c r="D253" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E253" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.015</v>
       </c>
       <c r="F253" s="0">
         <f>A253*200</f>
@@ -16708,10 +16672,10 @@
         <v/>
       </c>
       <c r="D254" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E254" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.015</v>
       </c>
       <c r="F254" s="0">
         <f>A254*200</f>
@@ -16762,10 +16726,10 @@
         <v/>
       </c>
       <c r="D255" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E255" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.015</v>
       </c>
       <c r="F255" s="0">
         <f>A255*200</f>
@@ -16816,10 +16780,10 @@
         <v/>
       </c>
       <c r="D256" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E256" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.015</v>
       </c>
       <c r="F256" s="0">
         <f>A256*200</f>
@@ -16870,10 +16834,10 @@
         <v/>
       </c>
       <c r="D257" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E257" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.015</v>
       </c>
       <c r="F257" s="0">
         <f>A257*200</f>
@@ -16924,10 +16888,10 @@
         <v/>
       </c>
       <c r="D258" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E258" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.015</v>
       </c>
       <c r="F258" s="0">
         <f>A258*200</f>
@@ -16978,10 +16942,10 @@
         <v/>
       </c>
       <c r="D259" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E259" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.015</v>
       </c>
       <c r="F259" s="0">
         <f>A259*200</f>
@@ -17032,10 +16996,10 @@
         <v/>
       </c>
       <c r="D260" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E260" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.015</v>
       </c>
       <c r="F260" s="0">
         <f>A260*200</f>
@@ -17086,10 +17050,10 @@
         <v/>
       </c>
       <c r="D261" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E261" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.015</v>
       </c>
       <c r="F261" s="0">
         <f>A261*200</f>
@@ -17140,10 +17104,10 @@
         <v/>
       </c>
       <c r="D262" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E262" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.015</v>
       </c>
       <c r="F262" s="0">
         <f>A262*200</f>
@@ -17194,10 +17158,10 @@
         <v/>
       </c>
       <c r="D263" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E263" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.015</v>
       </c>
       <c r="F263" s="0">
         <f>A263*200</f>
@@ -17248,10 +17212,10 @@
         <v/>
       </c>
       <c r="D264" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E264" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.015</v>
       </c>
       <c r="F264" s="0">
         <f>A264*200</f>
@@ -17302,10 +17266,10 @@
         <v/>
       </c>
       <c r="D265" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E265" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.015</v>
       </c>
       <c r="F265" s="0">
         <f>A265*200</f>
@@ -17356,10 +17320,10 @@
         <v/>
       </c>
       <c r="D266" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E266" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.015</v>
       </c>
       <c r="F266" s="0">
         <f>A266*200</f>
@@ -17410,10 +17374,10 @@
         <v/>
       </c>
       <c r="D267" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E267" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.015</v>
       </c>
       <c r="F267" s="0">
         <f>A267*200</f>
@@ -17464,10 +17428,10 @@
         <v/>
       </c>
       <c r="D268" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E268" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.015</v>
       </c>
       <c r="F268" s="0">
         <f>A268*200</f>
@@ -17518,10 +17482,10 @@
         <v/>
       </c>
       <c r="D269" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E269" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.015</v>
       </c>
       <c r="F269" s="0">
         <f>A269*200</f>
@@ -17572,10 +17536,10 @@
         <v/>
       </c>
       <c r="D270" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E270" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.015</v>
       </c>
       <c r="F270" s="0">
         <f>A270*200</f>
@@ -17626,10 +17590,10 @@
         <v/>
       </c>
       <c r="D271" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E271" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.015</v>
       </c>
       <c r="F271" s="0">
         <f>A271*200</f>
@@ -17680,10 +17644,10 @@
         <v/>
       </c>
       <c r="D272" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E272" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.015</v>
       </c>
       <c r="F272" s="0">
         <f>A272*200</f>
@@ -17734,10 +17698,10 @@
         <v/>
       </c>
       <c r="D273" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E273" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.015</v>
       </c>
       <c r="F273" s="0">
         <f>A273*200</f>
@@ -17788,10 +17752,10 @@
         <v/>
       </c>
       <c r="D274" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E274" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.015</v>
       </c>
       <c r="F274" s="0">
         <f>A274*200</f>
@@ -17842,10 +17806,10 @@
         <v/>
       </c>
       <c r="D275" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E275" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.015</v>
       </c>
       <c r="F275" s="0">
         <f>A275*200</f>
@@ -17896,10 +17860,10 @@
         <v/>
       </c>
       <c r="D276" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E276" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.015</v>
       </c>
       <c r="F276" s="0">
         <f>A276*200</f>
@@ -17950,10 +17914,10 @@
         <v/>
       </c>
       <c r="D277" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E277" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.015</v>
       </c>
       <c r="F277" s="0">
         <f>A277*200</f>
@@ -18004,10 +17968,10 @@
         <v/>
       </c>
       <c r="D278" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E278" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.015</v>
       </c>
       <c r="F278" s="0">
         <f>A278*200</f>
@@ -18058,10 +18022,10 @@
         <v/>
       </c>
       <c r="D279" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E279" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.015</v>
       </c>
       <c r="F279" s="0">
         <f>A279*200</f>
@@ -18112,10 +18076,10 @@
         <v/>
       </c>
       <c r="D280" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E280" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.015</v>
       </c>
       <c r="F280" s="0">
         <f>A280*200</f>
@@ -18166,10 +18130,10 @@
         <v/>
       </c>
       <c r="D281" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E281" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.015</v>
       </c>
       <c r="F281" s="0">
         <f>A281*200</f>
@@ -18220,10 +18184,10 @@
         <v/>
       </c>
       <c r="D282" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E282" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.015</v>
       </c>
       <c r="F282" s="0">
         <f>A282*200</f>
@@ -18274,10 +18238,10 @@
         <v/>
       </c>
       <c r="D283" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E283" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.015</v>
       </c>
       <c r="F283" s="0">
         <f>A283*200</f>
@@ -18328,10 +18292,10 @@
         <v/>
       </c>
       <c r="D284" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E284" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.015</v>
       </c>
       <c r="F284" s="0">
         <f>A284*200</f>
@@ -18382,10 +18346,10 @@
         <v/>
       </c>
       <c r="D285" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E285" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.015</v>
       </c>
       <c r="F285" s="0">
         <f>A285*200</f>
@@ -18436,10 +18400,10 @@
         <v/>
       </c>
       <c r="D286" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E286" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.015</v>
       </c>
       <c r="F286" s="0">
         <f>A286*200</f>
@@ -18490,10 +18454,10 @@
         <v/>
       </c>
       <c r="D287" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E287" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.015</v>
       </c>
       <c r="F287" s="0">
         <f>A287*200</f>
@@ -18544,10 +18508,10 @@
         <v/>
       </c>
       <c r="D288" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E288" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.015</v>
       </c>
       <c r="F288" s="0">
         <f>A288*200</f>
@@ -18598,10 +18562,10 @@
         <v/>
       </c>
       <c r="D289" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E289" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.015</v>
       </c>
       <c r="F289" s="0">
         <f>A289*200</f>
@@ -18652,10 +18616,10 @@
         <v/>
       </c>
       <c r="D290" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E290" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.015</v>
       </c>
       <c r="F290" s="0">
         <f>A290*200</f>
@@ -18706,10 +18670,10 @@
         <v/>
       </c>
       <c r="D291" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E291" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.015</v>
       </c>
       <c r="F291" s="0">
         <f>A291*200</f>
@@ -18760,10 +18724,10 @@
         <v/>
       </c>
       <c r="D292" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E292" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.015</v>
       </c>
       <c r="F292" s="0">
         <f>A292*200</f>
@@ -18814,10 +18778,10 @@
         <v/>
       </c>
       <c r="D293" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E293" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.015</v>
       </c>
       <c r="F293" s="0">
         <f>A293*200</f>
@@ -18868,10 +18832,10 @@
         <v/>
       </c>
       <c r="D294" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E294" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.015</v>
       </c>
       <c r="F294" s="0">
         <f>A294*200</f>
@@ -18922,10 +18886,10 @@
         <v/>
       </c>
       <c r="D295" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E295" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.015</v>
       </c>
       <c r="F295" s="0">
         <f>A295*200</f>
@@ -18976,10 +18940,10 @@
         <v/>
       </c>
       <c r="D296" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E296" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.015</v>
       </c>
       <c r="F296" s="0">
         <f>A296*200</f>
@@ -19030,10 +18994,10 @@
         <v/>
       </c>
       <c r="D297" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E297" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.015</v>
       </c>
       <c r="F297" s="0">
         <f>A297*200</f>
@@ -19084,10 +19048,10 @@
         <v/>
       </c>
       <c r="D298" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E298" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.015</v>
       </c>
       <c r="F298" s="0">
         <f>A298*200</f>
@@ -19138,10 +19102,10 @@
         <v/>
       </c>
       <c r="D299" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E299" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.015</v>
       </c>
       <c r="F299" s="0">
         <f>A299*200</f>
@@ -19192,10 +19156,10 @@
         <v/>
       </c>
       <c r="D300" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E300" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.015</v>
       </c>
       <c r="F300" s="0">
         <f>A300*200</f>
@@ -19246,10 +19210,10 @@
         <v/>
       </c>
       <c r="D301" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E301" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.015</v>
       </c>
       <c r="F301" s="0">
         <f>A301*200</f>
@@ -19300,10 +19264,10 @@
         <v/>
       </c>
       <c r="D302" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E302" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.015</v>
       </c>
       <c r="F302" s="0">
         <f>A302*200</f>
@@ -19354,10 +19318,10 @@
         <v/>
       </c>
       <c r="D303" s="0" t="n">
-        <v>0.0165</v>
+        <v>0.0173</v>
       </c>
       <c r="E303" s="0" t="n">
-        <v>0.01413</v>
+        <v>0.015</v>
       </c>
       <c r="F303" s="0">
         <f>A303*200</f>
